--- a/Minería de datos/Práctica 7/Episodios.xlsx
+++ b/Minería de datos/Práctica 7/Episodios.xlsx
@@ -1,27 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7ED3EC-54F4-443E-B322-554E274A8804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="71">
   <si>
     <t>Serie:</t>
   </si>
@@ -216,12 +228,30 @@
   </si>
   <si>
     <t xml:space="preserve">Guía </t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>A entonces B, Tal Ventana (Tamaño de la ventana)</t>
+  </si>
+  <si>
+    <t>Leer reglas de asociación.</t>
+  </si>
+  <si>
+    <t>No hacer reglas compuestas.</t>
+  </si>
+  <si>
+    <t>Leer y traer preguntas.</t>
+  </si>
+  <si>
+    <t>Variable de consecuente.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -375,39 +405,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -420,6 +428,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
     </xf>
@@ -457,7 +486,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1"/>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -500,7 +535,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1"/>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -788,19 +829,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E53"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -808,351 +849,337 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="E3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>6.9444444444444444E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="22"/>
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="4">
         <v>2.199074074074074E-4</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7" t="s">
+      <c r="E5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="22"/>
+      <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="4">
         <v>3.0324074074074073E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7" t="s">
+      <c r="E6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="22"/>
+      <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="4">
         <v>8.1249999999999985E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7" t="s">
+      <c r="E7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="22"/>
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="4">
         <v>8.9583333333333338E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7" t="s">
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="22"/>
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="8"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7" t="s">
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="22"/>
+      <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="22"/>
+      <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7" t="s">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="22"/>
+      <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="22"/>
+      <c r="B13" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="22"/>
+      <c r="B14" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="7"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7" t="s">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="22"/>
+      <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="22"/>
+      <c r="B16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="22"/>
+      <c r="B17" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="22"/>
+      <c r="B18" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="22"/>
+      <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="22"/>
+      <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="7"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="22"/>
+      <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="7"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="22"/>
+      <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="22"/>
+      <c r="B23" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="7"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="22"/>
+      <c r="B24" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="7"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="22"/>
+      <c r="B25" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="7"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="22"/>
+      <c r="B26" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="22"/>
+      <c r="B27" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="7"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="9"/>
-      <c r="B28" s="10" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="23"/>
+      <c r="B28" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="10"/>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="4"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7" t="s">
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="22"/>
+      <c r="B30" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="7"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="22"/>
+      <c r="B31" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="7"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="22"/>
+      <c r="B32" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="7"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7" t="s">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="22"/>
+      <c r="B33" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="7"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7" t="s">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="22"/>
+      <c r="B34" t="s">
         <v>22</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="4">
         <v>3.7268518518518514E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="22"/>
+      <c r="B35" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="4">
         <v>3.7268518518518514E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="22"/>
+      <c r="B36" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="4">
         <v>5.6944444444444438E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="22"/>
+      <c r="B37" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="7"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="6"/>
-      <c r="B38" s="7" t="s">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="22"/>
+      <c r="B38" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="7"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7" t="s">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="22"/>
+      <c r="B39" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="7"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7" t="s">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="22"/>
+      <c r="B40" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="7"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="6"/>
-      <c r="B41" s="7" t="s">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="22"/>
+      <c r="B41" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="7"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="6"/>
-      <c r="B42" s="7" t="s">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="22"/>
+      <c r="B42" t="s">
         <v>27</v>
       </c>
-      <c r="C42" s="7"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="6"/>
-      <c r="B43" s="7" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="22"/>
+      <c r="B43" t="s">
         <v>28</v>
       </c>
-      <c r="C43" s="7"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="9"/>
-      <c r="B44" s="10" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="23"/>
+      <c r="B44" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="10"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
+      <c r="C44" s="5"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1165,51 +1192,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:Q43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
+    <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="18" t="s">
+      <c r="C2" s="25"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="19">
+      <c r="B3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="11">
         <v>1</v>
       </c>
-      <c r="F3" s="23">
+      <c r="F3" s="15">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="7" t="s">
         <v>5</v>
       </c>
       <c r="M3" t="s">
@@ -1222,24 +1249,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="19">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="27"/>
+      <c r="B4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="11">
         <v>2</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="16">
         <v>2.199074074074074E-4</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="7" t="s">
         <v>36</v>
       </c>
       <c r="M4" t="s">
@@ -1252,24 +1279,24 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="19">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="27"/>
+      <c r="B5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="11">
         <v>3</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="16">
         <v>3.0324074074074073E-3</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M5" t="s">
@@ -1282,24 +1309,24 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="11" t="s">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="27"/>
+      <c r="B6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="19">
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="11">
         <v>4</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="16">
         <v>8.1249999999999985E-3</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="7" t="s">
         <v>56</v>
       </c>
       <c r="M6" t="s">
@@ -1309,24 +1336,24 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="19">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="27"/>
+      <c r="B7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="11">
         <v>5</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="16">
         <v>8.9583333333333338E-3</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M7" t="s">
@@ -1339,22 +1366,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="28"/>
-      <c r="B8" s="11" t="s">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="27"/>
+      <c r="B8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="19">
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="11">
         <v>6</v>
       </c>
-      <c r="F8" s="24"/>
-      <c r="G8" s="12" t="s">
+      <c r="F8" s="16"/>
+      <c r="G8" s="7" t="s">
         <v>56</v>
       </c>
       <c r="M8" t="s">
@@ -1364,22 +1391,22 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="11" t="s">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="27"/>
+      <c r="B9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="19">
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="11">
         <v>7</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12" t="s">
+      <c r="F9" s="6"/>
+      <c r="G9" s="7" t="s">
         <v>57</v>
       </c>
       <c r="M9" t="s">
@@ -1389,22 +1416,22 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
-      <c r="B10" s="11" t="s">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="27"/>
+      <c r="B10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="19">
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="11">
         <v>8</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12" t="s">
+      <c r="F10" s="6"/>
+      <c r="G10" s="7" t="s">
         <v>58</v>
       </c>
       <c r="M10" t="s">
@@ -1414,22 +1441,22 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="11" t="s">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="27"/>
+      <c r="B11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="19">
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="11">
         <v>9</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12" t="s">
+      <c r="F11" s="6"/>
+      <c r="G11" s="7" t="s">
         <v>57</v>
       </c>
       <c r="M11" t="s">
@@ -1439,22 +1466,22 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-      <c r="B12" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="19">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="27"/>
+      <c r="B12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="11">
         <v>10</v>
       </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12" t="s">
+      <c r="F12" s="6"/>
+      <c r="G12" s="7" t="s">
         <v>36</v>
       </c>
       <c r="M12" t="s">
@@ -1467,22 +1494,22 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="19">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="27"/>
+      <c r="B13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="11">
         <v>11</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12" t="s">
+      <c r="F13" s="6"/>
+      <c r="G13" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M13" t="s">
@@ -1495,22 +1522,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
-      <c r="B14" s="11" t="s">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="27"/>
+      <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="19">
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="11">
         <v>12</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12" t="s">
+      <c r="F14" s="6"/>
+      <c r="G14" s="7" t="s">
         <v>57</v>
       </c>
       <c r="M14" t="s">
@@ -1520,22 +1547,22 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="19">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="27"/>
+      <c r="B15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="11">
         <v>13</v>
       </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12" t="s">
+      <c r="F15" s="6"/>
+      <c r="G15" s="7" t="s">
         <v>59</v>
       </c>
       <c r="M15" t="s">
@@ -1545,22 +1572,22 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
-      <c r="B16" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="19">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="27"/>
+      <c r="B16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="11">
         <v>14</v>
       </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="12" t="s">
+      <c r="F16" s="6"/>
+      <c r="G16" s="7" t="s">
         <v>36</v>
       </c>
       <c r="M16" t="s">
@@ -1573,22 +1600,22 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="19">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="27"/>
+      <c r="B17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="11">
         <v>15</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="12" t="s">
+      <c r="F17" s="6"/>
+      <c r="G17" s="7" t="s">
         <v>60</v>
       </c>
       <c r="M17" t="s">
@@ -1598,22 +1625,22 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
-      <c r="B18" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" s="19">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" s="27"/>
+      <c r="B18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="11">
         <v>16</v>
       </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="12" t="s">
+      <c r="F18" s="6"/>
+      <c r="G18" s="7" t="s">
         <v>44</v>
       </c>
       <c r="M18" t="s">
@@ -1632,22 +1659,22 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="19">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" s="27"/>
+      <c r="B19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="11">
         <v>17</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="12" t="s">
+      <c r="F19" s="6"/>
+      <c r="G19" s="7" t="s">
         <v>47</v>
       </c>
       <c r="M19" t="s">
@@ -1660,22 +1687,22 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="28"/>
-      <c r="B20" s="11" t="s">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" s="27"/>
+      <c r="B20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="19">
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="11">
         <v>18</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="12" t="s">
+      <c r="F20" s="6"/>
+      <c r="G20" s="7" t="s">
         <v>61</v>
       </c>
       <c r="M20" t="s">
@@ -1685,22 +1712,22 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="19">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" s="27"/>
+      <c r="B21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="11">
         <v>19</v>
       </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12" t="s">
+      <c r="F21" s="6"/>
+      <c r="G21" s="7" t="s">
         <v>47</v>
       </c>
       <c r="M21" t="s">
@@ -1713,22 +1740,22 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="28"/>
-      <c r="B22" s="11" t="s">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" s="27"/>
+      <c r="B22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E22" s="19">
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="11">
         <v>20</v>
       </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12" t="s">
+      <c r="F22" s="6"/>
+      <c r="G22" s="7" t="s">
         <v>56</v>
       </c>
       <c r="M22" t="s">
@@ -1738,22 +1765,22 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
-      <c r="B23" s="11" t="s">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" s="27"/>
+      <c r="B23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="19">
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="11">
         <v>21</v>
       </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="12" t="s">
+      <c r="F23" s="6"/>
+      <c r="G23" s="7" t="s">
         <v>57</v>
       </c>
       <c r="M23" t="s">
@@ -1763,22 +1790,22 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="28"/>
-      <c r="B24" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" s="19">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24" s="27"/>
+      <c r="B24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="11">
         <v>22</v>
       </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="12" t="s">
+      <c r="F24" s="6"/>
+      <c r="G24" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M24" t="s">
@@ -1791,22 +1818,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
-      <c r="B25" s="11" t="s">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" s="27"/>
+      <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E25" s="19">
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" s="11">
         <v>23</v>
       </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="12" t="s">
+      <c r="F25" s="6"/>
+      <c r="G25" s="7" t="s">
         <v>57</v>
       </c>
       <c r="M25" t="s">
@@ -1816,22 +1843,22 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="28"/>
-      <c r="B26" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" s="19">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26" s="27"/>
+      <c r="B26" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="11">
         <v>24</v>
       </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="12" t="s">
+      <c r="F26" s="6"/>
+      <c r="G26" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M26" t="s">
@@ -1844,22 +1871,22 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
-      <c r="B27" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" s="19">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A27" s="27"/>
+      <c r="B27" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="11">
         <v>25</v>
       </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="12" t="s">
+      <c r="F27" s="6"/>
+      <c r="G27" s="7" t="s">
         <v>47</v>
       </c>
       <c r="M27" t="s">
@@ -1872,24 +1899,24 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B28" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="E28" s="27">
+      <c r="B28" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="19">
         <v>26</v>
       </c>
-      <c r="F28" s="25"/>
-      <c r="G28" s="26" t="s">
+      <c r="F28" s="17"/>
+      <c r="G28" s="18" t="s">
         <v>59</v>
       </c>
       <c r="M28" t="s">
@@ -1899,22 +1926,22 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
-      <c r="B29" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E29" s="19">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" s="27"/>
+      <c r="B29" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="11">
         <v>27</v>
       </c>
-      <c r="F29" s="11"/>
-      <c r="G29" s="12" t="s">
+      <c r="F29" s="6"/>
+      <c r="G29" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M29" t="s">
@@ -1927,22 +1954,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="28"/>
-      <c r="B30" s="11" t="s">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A30" s="27"/>
+      <c r="B30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E30" s="19">
+      <c r="C30" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" s="11">
         <v>28</v>
       </c>
-      <c r="F30" s="11"/>
-      <c r="G30" s="12" t="s">
+      <c r="F30" s="6"/>
+      <c r="G30" s="7" t="s">
         <v>56</v>
       </c>
       <c r="M30" t="s">
@@ -1952,22 +1979,22 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="28"/>
-      <c r="B31" s="11" t="s">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31" s="27"/>
+      <c r="B31" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" s="19">
+      <c r="C31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="11">
         <v>29</v>
       </c>
-      <c r="F31" s="11"/>
-      <c r="G31" s="12" t="s">
+      <c r="F31" s="6"/>
+      <c r="G31" s="7" t="s">
         <v>58</v>
       </c>
       <c r="M31" t="s">
@@ -1977,22 +2004,22 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="28"/>
-      <c r="B32" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" s="19">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A32" s="27"/>
+      <c r="B32" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" s="11">
         <v>30</v>
       </c>
-      <c r="F32" s="11"/>
-      <c r="G32" s="12" t="s">
+      <c r="F32" s="6"/>
+      <c r="G32" s="7" t="s">
         <v>47</v>
       </c>
       <c r="M32" t="s">
@@ -2005,24 +2032,24 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
-      <c r="B33" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E33" s="19">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A33" s="27"/>
+      <c r="B33" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="11">
         <v>31</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="16">
         <v>3.7268518518518514E-3</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="7" t="s">
         <v>62</v>
       </c>
       <c r="M33" t="s">
@@ -2032,24 +2059,24 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="28"/>
-      <c r="B34" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E34" s="19">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A34" s="27"/>
+      <c r="B34" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="11">
         <v>31</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="16">
         <v>3.7268518518518514E-3</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="7" t="s">
         <v>62</v>
       </c>
       <c r="M34" t="s">
@@ -2059,24 +2086,24 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
-      <c r="B35" s="11" t="s">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A35" s="27"/>
+      <c r="B35" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="19">
+      <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="11">
         <v>32</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="16">
         <v>5.6944444444444438E-3</v>
       </c>
-      <c r="G35" s="12" t="s">
+      <c r="G35" s="7" t="s">
         <v>58</v>
       </c>
       <c r="M35" t="s">
@@ -2086,22 +2113,22 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
-      <c r="B36" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="19">
-        <v>34</v>
-      </c>
-      <c r="F36" s="11"/>
-      <c r="G36" s="12" t="s">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A36" s="27"/>
+      <c r="B36" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="11">
+        <v>34</v>
+      </c>
+      <c r="F36" s="6"/>
+      <c r="G36" s="7" t="s">
         <v>44</v>
       </c>
       <c r="M36" t="s">
@@ -2120,22 +2147,22 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="28"/>
-      <c r="B37" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E37" s="19">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A37" s="27"/>
+      <c r="B37" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="11">
         <v>35</v>
       </c>
-      <c r="F37" s="11"/>
-      <c r="G37" s="12" t="s">
+      <c r="F37" s="6"/>
+      <c r="G37" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M37" t="s">
@@ -2148,22 +2175,22 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="28"/>
-      <c r="B38" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" s="19">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A38" s="27"/>
+      <c r="B38" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="11">
         <v>36</v>
       </c>
-      <c r="F38" s="11"/>
-      <c r="G38" s="12" t="s">
+      <c r="F38" s="6"/>
+      <c r="G38" s="7" t="s">
         <v>47</v>
       </c>
       <c r="M38" t="s">
@@ -2176,22 +2203,22 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="28"/>
-      <c r="B39" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="19">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A39" s="27"/>
+      <c r="B39" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="11">
         <v>37</v>
       </c>
-      <c r="F39" s="11"/>
-      <c r="G39" s="12" t="s">
+      <c r="F39" s="6"/>
+      <c r="G39" s="7" t="s">
         <v>44</v>
       </c>
       <c r="M39" t="s">
@@ -2210,22 +2237,22 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" s="28"/>
-      <c r="B40" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="7" t="s">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A40" s="27"/>
+      <c r="B40" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E40" s="19">
+      <c r="D40" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="11">
         <v>38</v>
       </c>
-      <c r="F40" s="11"/>
-      <c r="G40" s="12" t="s">
+      <c r="F40" s="6"/>
+      <c r="G40" s="7" t="s">
         <v>47</v>
       </c>
       <c r="M40" t="s">
@@ -2238,22 +2265,22 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
-      <c r="B41" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E41" s="19">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A41" s="27"/>
+      <c r="B41" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E41" s="11">
         <v>39</v>
       </c>
-      <c r="F41" s="11"/>
-      <c r="G41" s="12" t="s">
+      <c r="F41" s="6"/>
+      <c r="G41" s="7" t="s">
         <v>49</v>
       </c>
       <c r="M41" t="s">
@@ -2266,22 +2293,22 @@
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="28"/>
-      <c r="B42" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E42" s="19">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A42" s="27"/>
+      <c r="B42" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="11">
         <v>40</v>
       </c>
-      <c r="F42" s="11"/>
-      <c r="G42" s="12" t="s">
+      <c r="F42" s="6"/>
+      <c r="G42" s="7" t="s">
         <v>63</v>
       </c>
       <c r="M42" t="s">
@@ -2291,22 +2318,22 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="28"/>
-      <c r="B43" s="16" t="s">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A43" s="27"/>
+      <c r="B43" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" s="20">
+      <c r="C43" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" s="12">
         <v>41</v>
       </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="12" t="s">
+      <c r="F43" s="8"/>
+      <c r="G43" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M43" t="s">
@@ -2329,10 +2356,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="B15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Minería de datos/Práctica 7/Episodios.xlsx
+++ b/Minería de datos/Práctica 7/Episodios.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA94F4E-A533-4F2C-A7FD-FE83D47B6E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -867,7 +866,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1050,13 +1049,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1070,15 +1078,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1102,22 +1101,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1078675</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>128650</xdr:rowOff>
+      <xdr:colOff>629496</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>48439</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>130076</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>306539</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>45920</xdr:rowOff>
+      <xdr:rowOff>150194</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00BBC820-DF66-4871-97A4-C33F96BC4445}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00BBC820-DF66-4871-97A4-C33F96BC4445}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1133,8 +1132,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6660078" y="2088079"/>
-          <a:ext cx="7304751" cy="1876698"/>
+          <a:off x="6196107" y="2262250"/>
+          <a:ext cx="7313085" cy="1946597"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1166,7 +1165,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1457,7 +1456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q233"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1480,9 +1479,9 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
       <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -1498,12 +1497,12 @@
       <c r="L3" t="s">
         <v>258</v>
       </c>
-      <c r="M3" s="30" t="s">
+      <c r="M3" s="22" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1516,13 +1515,13 @@
       <c r="D4" s="2">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="E4" s="28"/>
+      <c r="E4" s="20"/>
       <c r="M4" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
+      <c r="A5" s="26"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -1539,7 +1538,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
+      <c r="A6" s="26"/>
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -1565,7 +1564,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
+      <c r="A7" s="26"/>
       <c r="B7" t="s">
         <v>9</v>
       </c>
@@ -1588,7 +1587,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="20"/>
+      <c r="A8" s="26"/>
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -1605,7 +1604,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
+      <c r="A9" s="26"/>
       <c r="B9" t="s">
         <v>19</v>
       </c>
@@ -1622,7 +1621,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
+      <c r="A10" s="26"/>
       <c r="B10" t="s">
         <v>12</v>
       </c>
@@ -1642,7 +1641,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="20"/>
+      <c r="A11" s="26"/>
       <c r="B11" t="s">
         <v>13</v>
       </c>
@@ -1659,7 +1658,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="20"/>
+      <c r="A12" s="26"/>
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -1676,7 +1675,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
+      <c r="A13" s="26"/>
       <c r="B13" t="s">
         <v>7</v>
       </c>
@@ -1690,7 +1689,7 @@
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="20"/>
+      <c r="A14" s="26"/>
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -1704,7 +1703,7 @@
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="20"/>
+      <c r="A15" s="26"/>
       <c r="B15" t="s">
         <v>12</v>
       </c>
@@ -1718,7 +1717,7 @@
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="20"/>
+      <c r="A16" s="26"/>
       <c r="B16" t="s">
         <v>14</v>
       </c>
@@ -1732,7 +1731,7 @@
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="20"/>
+      <c r="A17" s="26"/>
       <c r="B17" t="s">
         <v>7</v>
       </c>
@@ -1746,7 +1745,7 @@
       <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="20"/>
+      <c r="A18" s="26"/>
       <c r="B18" t="s">
         <v>15</v>
       </c>
@@ -1760,7 +1759,7 @@
       <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="20"/>
+      <c r="A19" s="26"/>
       <c r="B19" t="s">
         <v>16</v>
       </c>
@@ -1774,7 +1773,7 @@
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="20"/>
+      <c r="A20" s="26"/>
       <c r="B20" t="s">
         <v>17</v>
       </c>
@@ -1788,7 +1787,7 @@
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="20"/>
+      <c r="A21" s="26"/>
       <c r="B21" t="s">
         <v>18</v>
       </c>
@@ -1802,7 +1801,7 @@
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="20"/>
+      <c r="A22" s="26"/>
       <c r="B22" t="s">
         <v>17</v>
       </c>
@@ -1816,7 +1815,7 @@
       <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="20"/>
+      <c r="A23" s="26"/>
       <c r="B23" t="s">
         <v>19</v>
       </c>
@@ -1830,7 +1829,7 @@
       <c r="E23" s="3"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="20"/>
+      <c r="A24" s="26"/>
       <c r="B24" t="s">
         <v>12</v>
       </c>
@@ -1850,7 +1849,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="20"/>
+      <c r="A25" s="26"/>
       <c r="B25" t="s">
         <v>8</v>
       </c>
@@ -1870,7 +1869,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="20"/>
+      <c r="A26" s="26"/>
       <c r="B26" t="s">
         <v>12</v>
       </c>
@@ -1885,12 +1884,12 @@
       <c r="G26" t="s">
         <v>271</v>
       </c>
-      <c r="H26" s="31">
+      <c r="H26" s="23">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="20"/>
+      <c r="A27" s="26"/>
       <c r="B27" t="s">
         <v>20</v>
       </c>
@@ -1905,7 +1904,7 @@
       <c r="G27" t="s">
         <v>271</v>
       </c>
-      <c r="H27" s="31" t="s">
+      <c r="H27" s="23" t="s">
         <v>273</v>
       </c>
     </row>
@@ -1924,7 +1923,7 @@
       <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="25" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -1940,7 +1939,7 @@
       <c r="E29" s="3"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="20"/>
+      <c r="A30" s="26"/>
       <c r="B30" t="s">
         <v>8</v>
       </c>
@@ -1954,7 +1953,7 @@
       <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="20"/>
+      <c r="A31" s="26"/>
       <c r="B31" t="s">
         <v>9</v>
       </c>
@@ -1968,7 +1967,7 @@
       <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="20"/>
+      <c r="A32" s="26"/>
       <c r="B32" t="s">
         <v>23</v>
       </c>
@@ -1982,7 +1981,7 @@
       <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="20"/>
+      <c r="A33" s="26"/>
       <c r="B33" t="s">
         <v>17</v>
       </c>
@@ -1996,7 +1995,7 @@
       <c r="E33" s="3"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="20"/>
+      <c r="A34" s="26"/>
       <c r="B34" t="s">
         <v>21</v>
       </c>
@@ -2010,7 +2009,7 @@
       <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="20"/>
+      <c r="A35" s="26"/>
       <c r="B35" t="s">
         <v>22</v>
       </c>
@@ -2024,7 +2023,7 @@
       <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="20"/>
+      <c r="A36" s="26"/>
       <c r="B36" t="s">
         <v>23</v>
       </c>
@@ -2038,7 +2037,7 @@
       <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="20"/>
+      <c r="A37" s="26"/>
       <c r="B37" t="s">
         <v>82</v>
       </c>
@@ -2050,7 +2049,7 @@
       <c r="E37" s="3"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="20"/>
+      <c r="A38" s="26"/>
       <c r="B38" t="s">
         <v>123</v>
       </c>
@@ -2064,7 +2063,7 @@
       <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="20"/>
+      <c r="A39" s="26"/>
       <c r="B39" t="s">
         <v>20</v>
       </c>
@@ -2078,7 +2077,7 @@
       <c r="E39" s="3"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="20"/>
+      <c r="A40" s="26"/>
       <c r="B40" t="s">
         <v>17</v>
       </c>
@@ -2092,7 +2091,7 @@
       <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="20"/>
+      <c r="A41" s="26"/>
       <c r="B41" t="s">
         <v>82</v>
       </c>
@@ -2106,7 +2105,7 @@
       <c r="E41" s="3"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="20"/>
+      <c r="A42" s="26"/>
       <c r="B42" t="s">
         <v>114</v>
       </c>
@@ -2118,7 +2117,7 @@
       <c r="E42" s="3"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="20"/>
+      <c r="A43" s="26"/>
       <c r="B43" t="s">
         <v>142</v>
       </c>
@@ -2132,7 +2131,7 @@
       <c r="E43" s="3"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="20"/>
+      <c r="A44" s="26"/>
       <c r="B44" t="s">
         <v>20</v>
       </c>
@@ -2146,7 +2145,7 @@
       <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="20"/>
+      <c r="A45" s="26"/>
       <c r="B45" t="s">
         <v>24</v>
       </c>
@@ -2174,7 +2173,7 @@
       <c r="E46" s="3"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="25" t="s">
         <v>86</v>
       </c>
       <c r="B47" t="s">
@@ -2190,7 +2189,7 @@
       <c r="E47" s="3"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="20"/>
+      <c r="A48" s="26"/>
       <c r="B48" t="s">
         <v>67</v>
       </c>
@@ -2204,7 +2203,7 @@
       <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="20"/>
+      <c r="A49" s="26"/>
       <c r="B49" t="s">
         <v>68</v>
       </c>
@@ -2218,7 +2217,7 @@
       <c r="E49" s="3"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="20"/>
+      <c r="A50" s="26"/>
       <c r="B50" t="s">
         <v>23</v>
       </c>
@@ -2232,7 +2231,7 @@
       <c r="E50" s="3"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="20"/>
+      <c r="A51" s="26"/>
       <c r="B51" t="s">
         <v>143</v>
       </c>
@@ -2246,7 +2245,7 @@
       <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="20"/>
+      <c r="A52" s="26"/>
       <c r="B52" t="s">
         <v>66</v>
       </c>
@@ -2260,7 +2259,7 @@
       <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="20"/>
+      <c r="A53" s="26"/>
       <c r="B53" t="s">
         <v>15</v>
       </c>
@@ -2274,7 +2273,7 @@
       <c r="E53" s="3"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="20"/>
+      <c r="A54" s="26"/>
       <c r="B54" t="s">
         <v>69</v>
       </c>
@@ -2288,7 +2287,7 @@
       <c r="E54" s="3"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="20"/>
+      <c r="A55" s="26"/>
       <c r="B55" t="s">
         <v>144</v>
       </c>
@@ -2302,7 +2301,7 @@
       <c r="E55" s="3"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="20"/>
+      <c r="A56" s="26"/>
       <c r="B56" t="s">
         <v>143</v>
       </c>
@@ -2316,7 +2315,7 @@
       <c r="E56" s="3"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="20"/>
+      <c r="A57" s="26"/>
       <c r="B57" t="s">
         <v>70</v>
       </c>
@@ -2330,7 +2329,7 @@
       <c r="E57" s="3"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="20"/>
+      <c r="A58" s="26"/>
       <c r="B58" t="s">
         <v>71</v>
       </c>
@@ -2344,7 +2343,7 @@
       <c r="E58" s="3"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="20"/>
+      <c r="A59" s="26"/>
       <c r="B59" t="s">
         <v>72</v>
       </c>
@@ -2358,7 +2357,7 @@
       <c r="E59" s="3"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="20"/>
+      <c r="A60" s="26"/>
       <c r="B60" t="s">
         <v>66</v>
       </c>
@@ -2372,7 +2371,7 @@
       <c r="E60" s="3"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="20"/>
+      <c r="A61" s="26"/>
       <c r="B61" t="s">
         <v>73</v>
       </c>
@@ -2386,7 +2385,7 @@
       <c r="E61" s="3"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="20"/>
+      <c r="A62" s="26"/>
       <c r="B62" t="s">
         <v>67</v>
       </c>
@@ -2400,7 +2399,7 @@
       <c r="E62" s="3"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="20"/>
+      <c r="A63" s="26"/>
       <c r="B63" t="s">
         <v>74</v>
       </c>
@@ -2414,7 +2413,7 @@
       <c r="E63" s="3"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="20"/>
+      <c r="A64" s="26"/>
       <c r="B64" t="s">
         <v>75</v>
       </c>
@@ -2428,7 +2427,7 @@
       <c r="E64" s="3"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="20"/>
+      <c r="A65" s="26"/>
       <c r="B65" t="s">
         <v>76</v>
       </c>
@@ -2442,7 +2441,7 @@
       <c r="E65" s="3"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="20"/>
+      <c r="A66" s="26"/>
       <c r="B66" t="s">
         <v>114</v>
       </c>
@@ -2456,7 +2455,7 @@
       <c r="E66" s="3"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="20"/>
+      <c r="A67" s="26"/>
       <c r="B67" t="s">
         <v>77</v>
       </c>
@@ -2470,7 +2469,7 @@
       <c r="E67" s="3"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="20" t="s">
+      <c r="A68" s="26" t="s">
         <v>87</v>
       </c>
       <c r="B68" t="s">
@@ -2486,7 +2485,7 @@
       <c r="E68" s="3"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="20"/>
+      <c r="A69" s="26"/>
       <c r="B69" t="s">
         <v>78</v>
       </c>
@@ -2500,7 +2499,7 @@
       <c r="E69" s="3"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="20"/>
+      <c r="A70" s="26"/>
       <c r="B70" t="s">
         <v>9</v>
       </c>
@@ -2514,7 +2513,7 @@
       <c r="E70" s="3"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="20"/>
+      <c r="A71" s="26"/>
       <c r="B71" t="s">
         <v>145</v>
       </c>
@@ -2528,7 +2527,7 @@
       <c r="E71" s="3"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="20"/>
+      <c r="A72" s="26"/>
       <c r="B72" t="s">
         <v>146</v>
       </c>
@@ -2542,7 +2541,7 @@
       <c r="E72" s="3"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="20"/>
+      <c r="A73" s="26"/>
       <c r="B73" t="s">
         <v>113</v>
       </c>
@@ -2556,7 +2555,7 @@
       <c r="E73" s="3"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="20"/>
+      <c r="A74" s="26"/>
       <c r="B74" t="s">
         <v>114</v>
       </c>
@@ -2570,7 +2569,7 @@
       <c r="E74" s="3"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="20"/>
+      <c r="A75" s="26"/>
       <c r="B75" t="s">
         <v>19</v>
       </c>
@@ -2584,7 +2583,7 @@
       <c r="E75" s="3"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="20"/>
+      <c r="A76" s="26"/>
       <c r="B76" t="s">
         <v>114</v>
       </c>
@@ -2598,7 +2597,7 @@
       <c r="E76" s="3"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="20"/>
+      <c r="A77" s="26"/>
       <c r="B77" t="s">
         <v>7</v>
       </c>
@@ -2612,7 +2611,7 @@
       <c r="E77" s="3"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="20"/>
+      <c r="A78" s="26"/>
       <c r="B78" t="s">
         <v>80</v>
       </c>
@@ -2626,7 +2625,7 @@
       <c r="E78" s="3"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="20"/>
+      <c r="A79" s="26"/>
       <c r="B79" t="s">
         <v>79</v>
       </c>
@@ -2640,7 +2639,7 @@
       <c r="E79" s="3"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="20"/>
+      <c r="A80" s="26"/>
       <c r="B80" t="s">
         <v>147</v>
       </c>
@@ -2654,7 +2653,7 @@
       <c r="E80" s="3"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="20"/>
+      <c r="A81" s="26"/>
       <c r="B81" t="s">
         <v>19</v>
       </c>
@@ -2668,7 +2667,7 @@
       <c r="E81" s="3"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="20"/>
+      <c r="A82" s="26"/>
       <c r="B82" t="s">
         <v>81</v>
       </c>
@@ -2682,7 +2681,7 @@
       <c r="E82" s="3"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="20"/>
+      <c r="A83" s="26"/>
       <c r="B83" t="s">
         <v>76</v>
       </c>
@@ -2696,7 +2695,7 @@
       <c r="E83" s="3"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="20"/>
+      <c r="A84" s="26"/>
       <c r="B84" t="s">
         <v>82</v>
       </c>
@@ -2710,7 +2709,7 @@
       <c r="E84" s="3"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="20"/>
+      <c r="A85" s="26"/>
       <c r="B85" t="s">
         <v>83</v>
       </c>
@@ -2724,7 +2723,7 @@
       <c r="E85" s="3"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="20"/>
+      <c r="A86" s="26"/>
       <c r="B86" t="s">
         <v>84</v>
       </c>
@@ -2738,7 +2737,7 @@
       <c r="E86" s="3"/>
     </row>
     <row r="87" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="20" t="s">
+      <c r="A87" s="26" t="s">
         <v>91</v>
       </c>
       <c r="B87" t="s">
@@ -2754,7 +2753,7 @@
       <c r="E87" s="3"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="20"/>
+      <c r="A88" s="26"/>
       <c r="B88" t="s">
         <v>7</v>
       </c>
@@ -2768,7 +2767,7 @@
       <c r="E88" s="3"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="20"/>
+      <c r="A89" s="26"/>
       <c r="B89" t="s">
         <v>143</v>
       </c>
@@ -2782,7 +2781,7 @@
       <c r="E89" s="3"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="20"/>
+      <c r="A90" s="26"/>
       <c r="B90" t="s">
         <v>148</v>
       </c>
@@ -2796,7 +2795,7 @@
       <c r="E90" s="3"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="20"/>
+      <c r="A91" s="26"/>
       <c r="B91" t="s">
         <v>88</v>
       </c>
@@ -2810,7 +2809,7 @@
       <c r="E91" s="3"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="20"/>
+      <c r="A92" s="26"/>
       <c r="B92" t="s">
         <v>143</v>
       </c>
@@ -2824,7 +2823,7 @@
       <c r="E92" s="3"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="20"/>
+      <c r="A93" s="26"/>
       <c r="B93" t="s">
         <v>89</v>
       </c>
@@ -2838,7 +2837,7 @@
       <c r="E93" s="3"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="20"/>
+      <c r="A94" s="26"/>
       <c r="B94" t="s">
         <v>143</v>
       </c>
@@ -2852,7 +2851,7 @@
       <c r="E94" s="3"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="20"/>
+      <c r="A95" s="26"/>
       <c r="B95" t="s">
         <v>70</v>
       </c>
@@ -2866,7 +2865,7 @@
       <c r="E95" s="3"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="20"/>
+      <c r="A96" s="26"/>
       <c r="B96" t="s">
         <v>90</v>
       </c>
@@ -2880,7 +2879,7 @@
       <c r="E96" s="3"/>
     </row>
     <row r="97" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="20" t="s">
+      <c r="A97" s="26" t="s">
         <v>99</v>
       </c>
       <c r="B97" t="s">
@@ -2896,7 +2895,7 @@
       <c r="E97" s="3"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="20"/>
+      <c r="A98" s="26"/>
       <c r="B98" t="s">
         <v>67</v>
       </c>
@@ -2910,7 +2909,7 @@
       <c r="E98" s="3"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="20"/>
+      <c r="A99" s="26"/>
       <c r="B99" t="s">
         <v>76</v>
       </c>
@@ -2924,7 +2923,7 @@
       <c r="E99" s="3"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="20"/>
+      <c r="A100" s="26"/>
       <c r="B100" t="s">
         <v>143</v>
       </c>
@@ -2938,7 +2937,7 @@
       <c r="E100" s="3"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="20"/>
+      <c r="A101" s="26"/>
       <c r="B101" t="s">
         <v>8</v>
       </c>
@@ -2952,7 +2951,7 @@
       <c r="E101" s="3"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="20"/>
+      <c r="A102" s="26"/>
       <c r="B102" t="s">
         <v>93</v>
       </c>
@@ -2966,7 +2965,7 @@
       <c r="E102" s="3"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="20"/>
+      <c r="A103" s="26"/>
       <c r="B103" t="s">
         <v>92</v>
       </c>
@@ -2980,7 +2979,7 @@
       <c r="E103" s="3"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="20"/>
+      <c r="A104" s="26"/>
       <c r="B104" t="s">
         <v>23</v>
       </c>
@@ -2994,7 +2993,7 @@
       <c r="E104" s="3"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="20"/>
+      <c r="A105" s="26"/>
       <c r="B105" t="s">
         <v>149</v>
       </c>
@@ -3008,7 +3007,7 @@
       <c r="E105" s="3"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="20"/>
+      <c r="A106" s="26"/>
       <c r="B106" t="s">
         <v>150</v>
       </c>
@@ -3022,7 +3021,7 @@
       <c r="E106" s="3"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="20"/>
+      <c r="A107" s="26"/>
       <c r="B107" t="s">
         <v>94</v>
       </c>
@@ -3036,7 +3035,7 @@
       <c r="E107" s="3"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="20"/>
+      <c r="A108" s="26"/>
       <c r="B108" t="s">
         <v>95</v>
       </c>
@@ -3050,7 +3049,7 @@
       <c r="E108" s="3"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="20"/>
+      <c r="A109" s="26"/>
       <c r="B109" t="s">
         <v>151</v>
       </c>
@@ -3064,7 +3063,7 @@
       <c r="E109" s="3"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="20"/>
+      <c r="A110" s="26"/>
       <c r="B110" t="s">
         <v>96</v>
       </c>
@@ -3078,7 +3077,7 @@
       <c r="E110" s="3"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="20"/>
+      <c r="A111" s="26"/>
       <c r="B111" t="s">
         <v>97</v>
       </c>
@@ -3092,7 +3091,7 @@
       <c r="E111" s="3"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="20"/>
+      <c r="A112" s="26"/>
       <c r="B112" t="s">
         <v>152</v>
       </c>
@@ -3106,7 +3105,7 @@
       <c r="E112" s="3"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="20"/>
+      <c r="A113" s="26"/>
       <c r="B113" t="s">
         <v>98</v>
       </c>
@@ -3120,7 +3119,7 @@
       <c r="E113" s="3"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="20"/>
+      <c r="A114" s="26"/>
       <c r="B114" t="s">
         <v>76</v>
       </c>
@@ -3134,7 +3133,7 @@
       <c r="E114" s="3"/>
     </row>
     <row r="115" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="20" t="s">
+      <c r="A115" s="26" t="s">
         <v>109</v>
       </c>
       <c r="B115" t="s">
@@ -3150,7 +3149,7 @@
       <c r="E115" s="3"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" s="20"/>
+      <c r="A116" s="26"/>
       <c r="B116" t="s">
         <v>8</v>
       </c>
@@ -3164,7 +3163,7 @@
       <c r="E116" s="3"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="20"/>
+      <c r="A117" s="26"/>
       <c r="B117" t="s">
         <v>100</v>
       </c>
@@ -3178,7 +3177,7 @@
       <c r="E117" s="3"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="20"/>
+      <c r="A118" s="26"/>
       <c r="B118" t="s">
         <v>19</v>
       </c>
@@ -3192,7 +3191,7 @@
       <c r="E118" s="3"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="20"/>
+      <c r="A119" s="26"/>
       <c r="B119" t="s">
         <v>12</v>
       </c>
@@ -3206,7 +3205,7 @@
       <c r="E119" s="3"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="20"/>
+      <c r="A120" s="26"/>
       <c r="B120" t="s">
         <v>101</v>
       </c>
@@ -3220,7 +3219,7 @@
       <c r="E120" s="3"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="20"/>
+      <c r="A121" s="26"/>
       <c r="B121" t="s">
         <v>12</v>
       </c>
@@ -3234,7 +3233,7 @@
       <c r="E121" s="3"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="20"/>
+      <c r="A122" s="26"/>
       <c r="B122" t="s">
         <v>17</v>
       </c>
@@ -3248,7 +3247,7 @@
       <c r="E122" s="3"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="20"/>
+      <c r="A123" s="26"/>
       <c r="B123" t="s">
         <v>82</v>
       </c>
@@ -3262,7 +3261,7 @@
       <c r="E123" s="3"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="20"/>
+      <c r="A124" s="26"/>
       <c r="B124" t="s">
         <v>102</v>
       </c>
@@ -3276,7 +3275,7 @@
       <c r="E124" s="3"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="20"/>
+      <c r="A125" s="26"/>
       <c r="B125" t="s">
         <v>94</v>
       </c>
@@ -3290,7 +3289,7 @@
       <c r="E125" s="3"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="20"/>
+      <c r="A126" s="26"/>
       <c r="B126" t="s">
         <v>22</v>
       </c>
@@ -3304,7 +3303,7 @@
       <c r="E126" s="3"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="20"/>
+      <c r="A127" s="26"/>
       <c r="B127" t="s">
         <v>103</v>
       </c>
@@ -3318,7 +3317,7 @@
       <c r="E127" s="3"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="20"/>
+      <c r="A128" s="26"/>
       <c r="B128" t="s">
         <v>104</v>
       </c>
@@ -3332,7 +3331,7 @@
       <c r="E128" s="3"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="20"/>
+      <c r="A129" s="26"/>
       <c r="B129" t="s">
         <v>70</v>
       </c>
@@ -3346,7 +3345,7 @@
       <c r="E129" s="3"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="20"/>
+      <c r="A130" s="26"/>
       <c r="B130" t="s">
         <v>93</v>
       </c>
@@ -3360,7 +3359,7 @@
       <c r="E130" s="3"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="20"/>
+      <c r="A131" s="26"/>
       <c r="B131" t="s">
         <v>71</v>
       </c>
@@ -3374,7 +3373,7 @@
       <c r="E131" s="3"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="20"/>
+      <c r="A132" s="26"/>
       <c r="B132" t="s">
         <v>105</v>
       </c>
@@ -3388,7 +3387,7 @@
       <c r="E132" s="3"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133" s="20"/>
+      <c r="A133" s="26"/>
       <c r="B133" t="s">
         <v>96</v>
       </c>
@@ -3402,7 +3401,7 @@
       <c r="E133" s="3"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" s="20"/>
+      <c r="A134" s="26"/>
       <c r="B134" t="s">
         <v>77</v>
       </c>
@@ -3416,7 +3415,7 @@
       <c r="E134" s="3"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" s="20"/>
+      <c r="A135" s="26"/>
       <c r="B135" t="s">
         <v>22</v>
       </c>
@@ -3430,7 +3429,7 @@
       <c r="E135" s="3"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A136" s="20"/>
+      <c r="A136" s="26"/>
       <c r="B136" t="s">
         <v>70</v>
       </c>
@@ -3444,7 +3443,7 @@
       <c r="E136" s="3"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A137" s="20"/>
+      <c r="A137" s="26"/>
       <c r="B137" t="s">
         <v>71</v>
       </c>
@@ -3458,7 +3457,7 @@
       <c r="E137" s="3"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" s="20"/>
+      <c r="A138" s="26"/>
       <c r="B138" t="s">
         <v>106</v>
       </c>
@@ -3472,7 +3471,7 @@
       <c r="E138" s="3"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" s="20"/>
+      <c r="A139" s="26"/>
       <c r="B139" t="s">
         <v>107</v>
       </c>
@@ -3486,7 +3485,7 @@
       <c r="E139" s="3"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" s="20"/>
+      <c r="A140" s="26"/>
       <c r="B140" t="s">
         <v>76</v>
       </c>
@@ -3500,7 +3499,7 @@
       <c r="E140" s="3"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" s="20"/>
+      <c r="A141" s="26"/>
       <c r="B141" t="s">
         <v>77</v>
       </c>
@@ -3514,7 +3513,7 @@
       <c r="E141" s="3"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" s="20"/>
+      <c r="A142" s="26"/>
       <c r="B142" t="s">
         <v>78</v>
       </c>
@@ -3528,7 +3527,7 @@
       <c r="E142" s="3"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" s="20"/>
+      <c r="A143" s="26"/>
       <c r="B143" t="s">
         <v>7</v>
       </c>
@@ -3542,7 +3541,7 @@
       <c r="E143" s="3"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144" s="20"/>
+      <c r="A144" s="26"/>
       <c r="B144" t="s">
         <v>82</v>
       </c>
@@ -3556,7 +3555,7 @@
       <c r="E144" s="3"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="20"/>
+      <c r="A145" s="26"/>
       <c r="B145" t="s">
         <v>19</v>
       </c>
@@ -3570,7 +3569,7 @@
       <c r="E145" s="3"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" s="20"/>
+      <c r="A146" s="26"/>
       <c r="B146" t="s">
         <v>108</v>
       </c>
@@ -3584,7 +3583,7 @@
       <c r="E146" s="3"/>
     </row>
     <row r="147" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="20" t="s">
+      <c r="A147" s="26" t="s">
         <v>120</v>
       </c>
       <c r="B147" t="s">
@@ -3600,7 +3599,7 @@
       <c r="E147" s="3"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A148" s="20"/>
+      <c r="A148" s="26"/>
       <c r="B148" t="s">
         <v>7</v>
       </c>
@@ -3614,7 +3613,7 @@
       <c r="E148" s="3"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A149" s="20"/>
+      <c r="A149" s="26"/>
       <c r="B149" t="s">
         <v>110</v>
       </c>
@@ -3628,7 +3627,7 @@
       <c r="E149" s="3"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A150" s="20"/>
+      <c r="A150" s="26"/>
       <c r="B150" t="s">
         <v>8</v>
       </c>
@@ -3642,7 +3641,7 @@
       <c r="E150" s="3"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A151" s="20"/>
+      <c r="A151" s="26"/>
       <c r="B151" t="s">
         <v>111</v>
       </c>
@@ -3656,7 +3655,7 @@
       <c r="E151" s="3"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A152" s="20"/>
+      <c r="A152" s="26"/>
       <c r="B152" t="s">
         <v>112</v>
       </c>
@@ -3670,7 +3669,7 @@
       <c r="E152" s="3"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A153" s="20"/>
+      <c r="A153" s="26"/>
       <c r="B153" t="s">
         <v>113</v>
       </c>
@@ -3684,7 +3683,7 @@
       <c r="E153" s="3"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A154" s="20"/>
+      <c r="A154" s="26"/>
       <c r="B154" t="s">
         <v>114</v>
       </c>
@@ -3698,7 +3697,7 @@
       <c r="E154" s="3"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A155" s="20"/>
+      <c r="A155" s="26"/>
       <c r="B155" t="s">
         <v>67</v>
       </c>
@@ -3712,7 +3711,7 @@
       <c r="E155" s="3"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A156" s="20"/>
+      <c r="A156" s="26"/>
       <c r="B156" t="s">
         <v>107</v>
       </c>
@@ -3726,7 +3725,7 @@
       <c r="E156" s="3"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A157" s="20"/>
+      <c r="A157" s="26"/>
       <c r="B157" t="s">
         <v>153</v>
       </c>
@@ -3740,7 +3739,7 @@
       <c r="E157" s="3"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A158" s="20"/>
+      <c r="A158" s="26"/>
       <c r="B158" t="s">
         <v>115</v>
       </c>
@@ -3754,7 +3753,7 @@
       <c r="E158" s="3"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A159" s="20"/>
+      <c r="A159" s="26"/>
       <c r="B159" t="s">
         <v>116</v>
       </c>
@@ -3768,7 +3767,7 @@
       <c r="E159" s="3"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A160" s="20"/>
+      <c r="A160" s="26"/>
       <c r="B160" t="s">
         <v>82</v>
       </c>
@@ -3782,7 +3781,7 @@
       <c r="E160" s="3"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A161" s="20"/>
+      <c r="A161" s="26"/>
       <c r="B161" t="s">
         <v>117</v>
       </c>
@@ -3796,7 +3795,7 @@
       <c r="E161" s="3"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A162" s="20"/>
+      <c r="A162" s="26"/>
       <c r="B162" t="s">
         <v>7</v>
       </c>
@@ -3810,7 +3809,7 @@
       <c r="E162" s="3"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A163" s="20"/>
+      <c r="A163" s="26"/>
       <c r="B163" t="s">
         <v>118</v>
       </c>
@@ -3824,7 +3823,7 @@
       <c r="E163" s="3"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A164" s="20"/>
+      <c r="A164" s="26"/>
       <c r="B164" t="s">
         <v>119</v>
       </c>
@@ -3838,7 +3837,7 @@
       <c r="E164" s="3"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A165" s="20"/>
+      <c r="A165" s="26"/>
       <c r="B165" t="s">
         <v>9</v>
       </c>
@@ -3852,7 +3851,7 @@
       <c r="E165" s="3"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A166" s="20" t="s">
+      <c r="A166" s="26" t="s">
         <v>121</v>
       </c>
       <c r="B166" t="s">
@@ -3868,7 +3867,7 @@
       <c r="E166" s="3"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A167" s="20"/>
+      <c r="A167" s="26"/>
       <c r="B167" t="s">
         <v>7</v>
       </c>
@@ -3882,7 +3881,7 @@
       <c r="E167" s="3"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A168" s="20"/>
+      <c r="A168" s="26"/>
       <c r="B168" t="s">
         <v>123</v>
       </c>
@@ -3896,7 +3895,7 @@
       <c r="E168" s="3"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A169" s="20"/>
+      <c r="A169" s="26"/>
       <c r="B169" t="s">
         <v>124</v>
       </c>
@@ -3910,7 +3909,7 @@
       <c r="E169" s="3"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A170" s="20"/>
+      <c r="A170" s="26"/>
       <c r="B170" t="s">
         <v>125</v>
       </c>
@@ -3924,7 +3923,7 @@
       <c r="E170" s="3"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A171" s="20"/>
+      <c r="A171" s="26"/>
       <c r="B171" t="s">
         <v>7</v>
       </c>
@@ -3938,7 +3937,7 @@
       <c r="E171" s="3"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172" s="20"/>
+      <c r="A172" s="26"/>
       <c r="B172" t="s">
         <v>126</v>
       </c>
@@ -3952,7 +3951,7 @@
       <c r="E172" s="3"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A173" s="20"/>
+      <c r="A173" s="26"/>
       <c r="B173" t="s">
         <v>7</v>
       </c>
@@ -3966,7 +3965,7 @@
       <c r="E173" s="3"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174" s="20"/>
+      <c r="A174" s="26"/>
       <c r="B174" t="s">
         <v>8</v>
       </c>
@@ -3980,7 +3979,7 @@
       <c r="E174" s="3"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175" s="20"/>
+      <c r="A175" s="26"/>
       <c r="B175" t="s">
         <v>7</v>
       </c>
@@ -3994,7 +3993,7 @@
       <c r="E175" s="3"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176" s="20"/>
+      <c r="A176" s="26"/>
       <c r="B176" t="s">
         <v>8</v>
       </c>
@@ -4008,7 +4007,7 @@
       <c r="E176" s="3"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177" s="20"/>
+      <c r="A177" s="26"/>
       <c r="B177" t="s">
         <v>76</v>
       </c>
@@ -4022,7 +4021,7 @@
       <c r="E177" s="3"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A178" s="20"/>
+      <c r="A178" s="26"/>
       <c r="B178" t="s">
         <v>127</v>
       </c>
@@ -4036,7 +4035,7 @@
       <c r="E178" s="3"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A179" s="20"/>
+      <c r="A179" s="26"/>
       <c r="B179" t="s">
         <v>128</v>
       </c>
@@ -4050,7 +4049,7 @@
       <c r="E179" s="3"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180" s="20"/>
+      <c r="A180" s="26"/>
       <c r="B180" t="s">
         <v>126</v>
       </c>
@@ -4064,7 +4063,7 @@
       <c r="E180" s="3"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A181" s="20"/>
+      <c r="A181" s="26"/>
       <c r="B181" t="s">
         <v>129</v>
       </c>
@@ -4078,7 +4077,7 @@
       <c r="E181" s="3"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182" s="20"/>
+      <c r="A182" s="26"/>
       <c r="B182" t="s">
         <v>7</v>
       </c>
@@ -4092,7 +4091,7 @@
       <c r="E182" s="3"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183" s="20"/>
+      <c r="A183" s="26"/>
       <c r="B183" t="s">
         <v>130</v>
       </c>
@@ -4106,7 +4105,7 @@
       <c r="E183" s="3"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184" s="20"/>
+      <c r="A184" s="26"/>
       <c r="B184" t="s">
         <v>118</v>
       </c>
@@ -4120,7 +4119,7 @@
       <c r="E184" s="3"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A185" s="20"/>
+      <c r="A185" s="26"/>
       <c r="B185" t="s">
         <v>123</v>
       </c>
@@ -4134,7 +4133,7 @@
       <c r="E185" s="3"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A186" s="20"/>
+      <c r="A186" s="26"/>
       <c r="B186" t="s">
         <v>126</v>
       </c>
@@ -4148,7 +4147,7 @@
       <c r="E186" s="3"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A187" s="20"/>
+      <c r="A187" s="26"/>
       <c r="B187" t="s">
         <v>131</v>
       </c>
@@ -4162,7 +4161,7 @@
       <c r="E187" s="3"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188" s="20"/>
+      <c r="A188" s="26"/>
       <c r="B188" t="s">
         <v>76</v>
       </c>
@@ -4176,7 +4175,7 @@
       <c r="E188" s="3"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A189" s="20"/>
+      <c r="A189" s="26"/>
       <c r="B189" t="s">
         <v>7</v>
       </c>
@@ -4190,7 +4189,7 @@
       <c r="E189" s="3"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A190" s="20"/>
+      <c r="A190" s="26"/>
       <c r="B190" t="s">
         <v>8</v>
       </c>
@@ -4204,7 +4203,7 @@
       <c r="E190" s="3"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A191" s="20"/>
+      <c r="A191" s="26"/>
       <c r="B191" t="s">
         <v>132</v>
       </c>
@@ -4218,7 +4217,7 @@
       <c r="E191" s="3"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A192" s="20"/>
+      <c r="A192" s="26"/>
       <c r="B192" t="s">
         <v>133</v>
       </c>
@@ -4232,7 +4231,7 @@
       <c r="E192" s="3"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A193" s="20"/>
+      <c r="A193" s="26"/>
       <c r="B193" t="s">
         <v>7</v>
       </c>
@@ -4246,7 +4245,7 @@
       <c r="E193" s="3"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A194" s="20"/>
+      <c r="A194" s="26"/>
       <c r="B194" t="s">
         <v>123</v>
       </c>
@@ -4260,7 +4259,7 @@
       <c r="E194" s="3"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A195" s="20"/>
+      <c r="A195" s="26"/>
       <c r="B195" t="s">
         <v>118</v>
       </c>
@@ -4274,7 +4273,7 @@
       <c r="E195" s="3"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A196" s="20"/>
+      <c r="A196" s="26"/>
       <c r="B196" t="s">
         <v>154</v>
       </c>
@@ -4288,7 +4287,7 @@
       <c r="E196" s="3"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A197" s="20"/>
+      <c r="A197" s="26"/>
       <c r="B197" t="s">
         <v>125</v>
       </c>
@@ -4302,7 +4301,7 @@
       <c r="E197" s="3"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A198" s="20"/>
+      <c r="A198" s="26"/>
       <c r="B198" t="s">
         <v>134</v>
       </c>
@@ -4316,7 +4315,7 @@
       <c r="E198" s="3"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A199" s="20"/>
+      <c r="A199" s="26"/>
       <c r="B199" t="s">
         <v>135</v>
       </c>
@@ -4330,7 +4329,7 @@
       <c r="E199" s="3"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A200" s="20"/>
+      <c r="A200" s="26"/>
       <c r="B200" t="s">
         <v>136</v>
       </c>
@@ -4344,7 +4343,7 @@
       <c r="E200" s="3"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A201" s="20"/>
+      <c r="A201" s="26"/>
       <c r="B201" t="s">
         <v>117</v>
       </c>
@@ -4358,7 +4357,7 @@
       <c r="E201" s="3"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A202" s="20"/>
+      <c r="A202" s="26"/>
       <c r="B202" t="s">
         <v>155</v>
       </c>
@@ -4372,7 +4371,7 @@
       <c r="E202" s="3"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A203" s="20"/>
+      <c r="A203" s="26"/>
       <c r="B203" t="s">
         <v>143</v>
       </c>
@@ -4386,7 +4385,7 @@
       <c r="E203" s="3"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A204" s="20"/>
+      <c r="A204" s="26"/>
       <c r="B204" t="s">
         <v>23</v>
       </c>
@@ -4400,7 +4399,7 @@
       <c r="E204" s="3"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A205" s="20"/>
+      <c r="A205" s="26"/>
       <c r="B205" t="s">
         <v>156</v>
       </c>
@@ -4414,7 +4413,7 @@
       <c r="E205" s="3"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A206" s="20"/>
+      <c r="A206" s="26"/>
       <c r="B206" t="s">
         <v>19</v>
       </c>
@@ -4428,7 +4427,7 @@
       <c r="E206" s="3"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A207" s="20"/>
+      <c r="A207" s="26"/>
       <c r="B207" t="s">
         <v>137</v>
       </c>
@@ -4442,7 +4441,7 @@
       <c r="E207" s="3"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A208" s="20"/>
+      <c r="A208" s="26"/>
       <c r="B208" t="s">
         <v>82</v>
       </c>
@@ -4456,7 +4455,7 @@
       <c r="E208" s="3"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A209" s="20"/>
+      <c r="A209" s="26"/>
       <c r="B209" t="s">
         <v>138</v>
       </c>
@@ -4470,7 +4469,7 @@
       <c r="E209" s="3"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A210" s="20"/>
+      <c r="A210" s="26"/>
       <c r="B210" t="s">
         <v>135</v>
       </c>
@@ -4484,7 +4483,7 @@
       <c r="E210" s="3"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A211" s="20"/>
+      <c r="A211" s="26"/>
       <c r="B211" t="s">
         <v>139</v>
       </c>
@@ -4498,7 +4497,7 @@
       <c r="E211" s="3"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A212" s="20"/>
+      <c r="A212" s="26"/>
       <c r="B212" t="s">
         <v>135</v>
       </c>
@@ -4512,7 +4511,7 @@
       <c r="E212" s="3"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A213" s="20"/>
+      <c r="A213" s="26"/>
       <c r="B213" t="s">
         <v>140</v>
       </c>
@@ -4526,7 +4525,7 @@
       <c r="E213" s="3"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A214" s="20"/>
+      <c r="A214" s="26"/>
       <c r="B214" t="s">
         <v>136</v>
       </c>
@@ -4540,7 +4539,7 @@
       <c r="E214" s="3"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A215" s="20"/>
+      <c r="A215" s="26"/>
       <c r="B215" t="s">
         <v>7</v>
       </c>
@@ -4554,7 +4553,7 @@
       <c r="E215" s="3"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A216" s="20"/>
+      <c r="A216" s="26"/>
       <c r="B216" t="s">
         <v>82</v>
       </c>
@@ -4568,7 +4567,7 @@
       <c r="E216" s="3"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A217" s="20"/>
+      <c r="A217" s="26"/>
       <c r="B217" t="s">
         <v>135</v>
       </c>
@@ -4582,7 +4581,7 @@
       <c r="E217" s="3"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A218" s="20"/>
+      <c r="A218" s="26"/>
       <c r="B218" t="s">
         <v>123</v>
       </c>
@@ -4596,7 +4595,7 @@
       <c r="E218" s="3"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A219" s="20"/>
+      <c r="A219" s="26"/>
       <c r="B219" t="s">
         <v>141</v>
       </c>
@@ -4610,7 +4609,7 @@
       <c r="E219" s="3"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A220" s="20"/>
+      <c r="A220" s="26"/>
       <c r="B220" t="s">
         <v>101</v>
       </c>
@@ -4624,7 +4623,7 @@
       <c r="E220" s="3"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A221" s="20"/>
+      <c r="A221" s="26"/>
       <c r="B221" t="s">
         <v>135</v>
       </c>
@@ -4638,7 +4637,7 @@
       <c r="E221" s="3"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A222" s="20"/>
+      <c r="A222" s="26"/>
       <c r="B222" t="s">
         <v>123</v>
       </c>
@@ -4652,7 +4651,7 @@
       <c r="E222" s="3"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A223" s="20"/>
+      <c r="A223" s="26"/>
       <c r="B223" t="s">
         <v>157</v>
       </c>
@@ -4666,7 +4665,7 @@
       <c r="E223" s="3"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A224" s="20"/>
+      <c r="A224" s="26"/>
       <c r="B224" t="s">
         <v>135</v>
       </c>
@@ -4680,7 +4679,7 @@
       <c r="E224" s="3"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A225" s="20"/>
+      <c r="A225" s="26"/>
       <c r="B225" t="s">
         <v>140</v>
       </c>
@@ -4694,7 +4693,7 @@
       <c r="E225" s="3"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A226" s="20"/>
+      <c r="A226" s="26"/>
       <c r="B226" t="s">
         <v>122</v>
       </c>
@@ -4708,7 +4707,7 @@
       <c r="E226" s="3"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A227" s="20"/>
+      <c r="A227" s="26"/>
       <c r="B227" t="s">
         <v>123</v>
       </c>
@@ -4722,7 +4721,7 @@
       <c r="E227" s="3"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A228" s="20"/>
+      <c r="A228" s="26"/>
       <c r="B228" t="s">
         <v>111</v>
       </c>
@@ -4736,7 +4735,7 @@
       <c r="E228" s="3"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A229" s="20"/>
+      <c r="A229" s="26"/>
       <c r="B229" t="s">
         <v>133</v>
       </c>
@@ -4750,7 +4749,7 @@
       <c r="E229" s="3"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A230" s="20"/>
+      <c r="A230" s="26"/>
       <c r="B230" t="s">
         <v>128</v>
       </c>
@@ -4764,7 +4763,7 @@
       <c r="E230" s="3"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A231" s="20"/>
+      <c r="A231" s="26"/>
       <c r="B231" t="s">
         <v>129</v>
       </c>
@@ -4778,7 +4777,7 @@
       <c r="E231" s="3"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A232" s="20"/>
+      <c r="A232" s="26"/>
       <c r="B232" t="s">
         <v>123</v>
       </c>
@@ -4792,7 +4791,7 @@
       <c r="E232" s="3"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A233" s="20"/>
+      <c r="A233" s="26"/>
       <c r="B233" t="s">
         <v>133</v>
       </c>
@@ -4807,17 +4806,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A166:A233"/>
+    <mergeCell ref="A87:A96"/>
+    <mergeCell ref="A97:A114"/>
+    <mergeCell ref="A147:A165"/>
+    <mergeCell ref="A115:A133"/>
+    <mergeCell ref="A134:A146"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A4:A28"/>
     <mergeCell ref="A29:A46"/>
     <mergeCell ref="A47:A67"/>
     <mergeCell ref="A68:A86"/>
-    <mergeCell ref="A87:A96"/>
-    <mergeCell ref="A97:A114"/>
-    <mergeCell ref="A147:A165"/>
-    <mergeCell ref="A115:A133"/>
-    <mergeCell ref="A134:A146"/>
-    <mergeCell ref="A166:A233"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4825,7 +4824,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:Q43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4835,11 +4834,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="9" t="s">
         <v>27</v>
       </c>
@@ -4851,7 +4850,7 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -4883,7 +4882,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="26"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="5" t="s">
         <v>30</v>
       </c>
@@ -4913,7 +4912,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="26"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="5" t="s">
         <v>29</v>
       </c>
@@ -4943,7 +4942,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="5" t="s">
         <v>34</v>
       </c>
@@ -4970,7 +4969,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="5" t="s">
         <v>29</v>
       </c>
@@ -5000,7 +4999,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
@@ -5025,7 +5024,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
@@ -5050,7 +5049,7 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
+      <c r="A10" s="31"/>
       <c r="B10" s="5" t="s">
         <v>11</v>
       </c>
@@ -5075,7 +5074,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
@@ -5100,7 +5099,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="5" t="s">
         <v>30</v>
       </c>
@@ -5128,7 +5127,7 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="5" t="s">
         <v>29</v>
       </c>
@@ -5156,7 +5155,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="26"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
@@ -5181,7 +5180,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="5" t="s">
         <v>29</v>
       </c>
@@ -5206,7 +5205,7 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="5" t="s">
         <v>30</v>
       </c>
@@ -5234,7 +5233,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
@@ -5259,7 +5258,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
+      <c r="A18" s="31"/>
       <c r="B18" s="5" t="s">
         <v>29</v>
       </c>
@@ -5293,7 +5292,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="5" t="s">
         <v>29</v>
       </c>
@@ -5321,7 +5320,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
@@ -5346,7 +5345,7 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="5" t="s">
         <v>29</v>
       </c>
@@ -5374,7 +5373,7 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="26"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
@@ -5399,7 +5398,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="26"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
@@ -5424,7 +5423,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="26"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="5" t="s">
         <v>29</v>
       </c>
@@ -5452,7 +5451,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="26"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
@@ -5477,7 +5476,7 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="26"/>
+      <c r="A26" s="31"/>
       <c r="B26" s="5" t="s">
         <v>30</v>
       </c>
@@ -5505,7 +5504,7 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="5" t="s">
         <v>29</v>
       </c>
@@ -5533,7 +5532,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="31" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="16" t="s">
@@ -5560,7 +5559,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="26"/>
+      <c r="A29" s="31"/>
       <c r="B29" s="5" t="s">
         <v>29</v>
       </c>
@@ -5588,7 +5587,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="5" t="s">
         <v>34</v>
       </c>
@@ -5613,7 +5612,7 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="26"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="5" t="s">
         <v>46</v>
       </c>
@@ -5638,7 +5637,7 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
+      <c r="A32" s="31"/>
       <c r="B32" s="5" t="s">
         <v>29</v>
       </c>
@@ -5666,7 +5665,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="26"/>
+      <c r="A33" s="31"/>
       <c r="B33" s="5" t="s">
         <v>30</v>
       </c>
@@ -5693,7 +5692,7 @@
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="26"/>
+      <c r="A34" s="31"/>
       <c r="B34" s="5" t="s">
         <v>29</v>
       </c>
@@ -5720,7 +5719,7 @@
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="26"/>
+      <c r="A35" s="31"/>
       <c r="B35" s="5" t="s">
         <v>34</v>
       </c>
@@ -5747,7 +5746,7 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" s="26"/>
+      <c r="A36" s="31"/>
       <c r="B36" s="5" t="s">
         <v>29</v>
       </c>
@@ -5781,7 +5780,7 @@
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A37" s="26"/>
+      <c r="A37" s="31"/>
       <c r="B37" s="5" t="s">
         <v>30</v>
       </c>
@@ -5809,7 +5808,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" s="26"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="5" t="s">
         <v>29</v>
       </c>
@@ -5837,7 +5836,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" s="26"/>
+      <c r="A39" s="31"/>
       <c r="B39" s="5" t="s">
         <v>29</v>
       </c>
@@ -5871,7 +5870,7 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="26"/>
+      <c r="A40" s="31"/>
       <c r="B40" s="5" t="s">
         <v>29</v>
       </c>
@@ -5899,7 +5898,7 @@
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="26"/>
+      <c r="A41" s="31"/>
       <c r="B41" s="5" t="s">
         <v>30</v>
       </c>
@@ -5927,7 +5926,7 @@
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="26"/>
+      <c r="A42" s="31"/>
       <c r="B42" s="5" t="s">
         <v>30</v>
       </c>
@@ -5952,7 +5951,7 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A43" s="26"/>
+      <c r="A43" s="31"/>
       <c r="B43" s="7" t="s">
         <v>34</v>
       </c>
@@ -5989,7 +5988,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:B100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6013,7 +6012,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="21" t="s">
         <v>85</v>
       </c>
       <c r="B4" t="s">
@@ -6053,7 +6052,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="21" t="s">
         <v>144</v>
       </c>
       <c r="B9" t="s">
@@ -6445,7 +6444,7 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="21" t="s">
         <v>6</v>
       </c>
       <c r="B58" t="s">
@@ -6557,7 +6556,7 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="29" t="s">
+      <c r="A72" s="21" t="s">
         <v>70</v>
       </c>
       <c r="B72" t="s">
@@ -6789,7 +6788,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B100">
+  <sortState ref="A2:B100">
     <sortCondition ref="A2:A100"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Minería de datos/Práctica 7/Episodios.xlsx
+++ b/Minería de datos/Práctica 7/Episodios.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AE2E6C-2790-4349-A8F3-0130112AEA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -805,9 +806,6 @@
     <t>E99</t>
   </si>
   <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
     <t>Dudas:</t>
   </si>
   <si>
@@ -861,12 +859,15 @@
   </si>
   <si>
     <t>Tenemos que terminar con una tabla así:</t>
+  </si>
+  <si>
+    <t>el support es por episodio</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1026,10 +1027,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1049,19 +1049,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1079,6 +1073,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="135" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1116,7 +1111,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00BBC820-DF66-4871-97A4-C33F96BC4445}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00BBC820-DF66-4871-97A4-C33F96BC4445}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1165,7 +1160,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1456,7 +1451,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q233"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1479,30 +1474,26 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="19"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="E2" s="18"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
-        <v>257</v>
-      </c>
       <c r="G3" t="s">
         <v>61</v>
       </c>
       <c r="L3" t="s">
+        <v>257</v>
+      </c>
+      <c r="M3" t="s">
         <v>258</v>
       </c>
-      <c r="M3" s="22" t="s">
-        <v>259</v>
-      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="21" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1512,16 +1503,13 @@
         <f>VLOOKUP(B4, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E57</v>
       </c>
-      <c r="D4" s="2">
-        <v>6.9444444444444444E-5</v>
-      </c>
-      <c r="E4" s="20"/>
+      <c r="E4" s="2"/>
       <c r="M4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="26"/>
+      <c r="A5" s="20"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -1529,16 +1517,15 @@
         <f>VLOOKUP(B5, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D5" s="3">
-        <v>2.199074074074074E-4</v>
-      </c>
-      <c r="E5" s="3"/>
+      <c r="E5" s="2" t="s">
+        <v>275</v>
+      </c>
       <c r="G5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
+      <c r="A6" s="20"/>
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -1546,25 +1533,22 @@
         <f>VLOOKUP(B6, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E47</v>
       </c>
-      <c r="D6" s="3">
-        <v>3.0324074074074073E-3</v>
-      </c>
-      <c r="E6" s="3"/>
+      <c r="E6" s="2"/>
       <c r="G6" t="s">
         <v>63</v>
       </c>
       <c r="M6" t="s">
+        <v>260</v>
+      </c>
+      <c r="P6" t="s">
         <v>261</v>
       </c>
-      <c r="P6" t="s">
-        <v>262</v>
-      </c>
       <c r="Q6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
+      <c r="A7" s="20"/>
       <c r="B7" t="s">
         <v>9</v>
       </c>
@@ -1572,22 +1556,19 @@
         <f>VLOOKUP(B7, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E7</v>
       </c>
-      <c r="D7" s="3">
-        <v>8.1249999999999985E-3</v>
-      </c>
-      <c r="E7" s="3"/>
+      <c r="E7" s="2"/>
       <c r="G7" t="s">
         <v>64</v>
       </c>
       <c r="P7" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q7" t="s">
         <v>263</v>
       </c>
-      <c r="Q7" t="s">
-        <v>264</v>
-      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
+      <c r="A8" s="20"/>
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -1595,16 +1576,13 @@
         <f>VLOOKUP(B8, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E47</v>
       </c>
-      <c r="D8" s="3">
-        <v>8.9583333333333338E-3</v>
-      </c>
-      <c r="E8" s="3"/>
+      <c r="E8" s="2"/>
       <c r="G8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
+      <c r="A9" s="20"/>
       <c r="B9" t="s">
         <v>19</v>
       </c>
@@ -1612,16 +1590,13 @@
         <f>VLOOKUP(B9, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E62</v>
       </c>
-      <c r="D9" s="3">
-        <v>5.0625000000000003E-2</v>
-      </c>
-      <c r="E9" s="3"/>
+      <c r="E9" s="2"/>
       <c r="M9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
+      <c r="A10" s="20"/>
       <c r="B10" t="s">
         <v>12</v>
       </c>
@@ -1629,19 +1604,16 @@
         <f>VLOOKUP(B10, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E61</v>
       </c>
-      <c r="D10" s="3">
-        <v>9.2291666666666702E-2</v>
-      </c>
-      <c r="E10" s="3"/>
+      <c r="E10" s="2"/>
       <c r="N10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
+      <c r="A11" s="20"/>
       <c r="B11" t="s">
         <v>13</v>
       </c>
@@ -1649,16 +1621,13 @@
         <f>VLOOKUP(B11, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E64</v>
       </c>
-      <c r="D11" s="3">
-        <v>0.13395833333333301</v>
-      </c>
-      <c r="E11" s="3"/>
+      <c r="E11" s="2"/>
       <c r="N11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
+      <c r="A12" s="20"/>
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -1666,16 +1635,13 @@
         <f>VLOOKUP(B12, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E61</v>
       </c>
-      <c r="D12" s="3">
-        <v>0.175625</v>
-      </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="2"/>
       <c r="N12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
+      <c r="A13" s="20"/>
       <c r="B13" t="s">
         <v>7</v>
       </c>
@@ -1683,13 +1649,10 @@
         <f>VLOOKUP(B13, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D13" s="3">
-        <v>0.21729166666666699</v>
-      </c>
-      <c r="E13" s="3"/>
+      <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="26"/>
+      <c r="A14" s="20"/>
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -1697,13 +1660,10 @@
         <f>VLOOKUP(B14, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E47</v>
       </c>
-      <c r="D14" s="3">
-        <v>0.25895833333333301</v>
-      </c>
-      <c r="E14" s="3"/>
+      <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
+      <c r="A15" s="20"/>
       <c r="B15" t="s">
         <v>12</v>
       </c>
@@ -1711,13 +1671,10 @@
         <f>VLOOKUP(B15, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E61</v>
       </c>
-      <c r="D15" s="3">
-        <v>0.30062499999999998</v>
-      </c>
-      <c r="E15" s="3"/>
+      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
+      <c r="A16" s="20"/>
       <c r="B16" t="s">
         <v>14</v>
       </c>
@@ -1725,13 +1682,10 @@
         <f>VLOOKUP(B16, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E34</v>
       </c>
-      <c r="D16" s="3">
-        <v>0.34229166666666699</v>
-      </c>
-      <c r="E16" s="3"/>
+      <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
+      <c r="A17" s="20"/>
       <c r="B17" t="s">
         <v>7</v>
       </c>
@@ -1739,13 +1693,10 @@
         <f>VLOOKUP(B17, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D17" s="3">
-        <v>0.38395833333333301</v>
-      </c>
-      <c r="E17" s="3"/>
+      <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
+      <c r="A18" s="20"/>
       <c r="B18" t="s">
         <v>15</v>
       </c>
@@ -1753,13 +1704,10 @@
         <f>VLOOKUP(B18, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E33</v>
       </c>
-      <c r="D18" s="3">
-        <v>0.42562499999999998</v>
-      </c>
-      <c r="E18" s="3"/>
+      <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
+      <c r="A19" s="20"/>
       <c r="B19" t="s">
         <v>16</v>
       </c>
@@ -1767,13 +1715,10 @@
         <f>VLOOKUP(B19, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E48</v>
       </c>
-      <c r="D19" s="3">
-        <v>0.46729166666666699</v>
-      </c>
-      <c r="E19" s="3"/>
+      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
+      <c r="A20" s="20"/>
       <c r="B20" t="s">
         <v>17</v>
       </c>
@@ -1781,13 +1726,10 @@
         <f>VLOOKUP(B20, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D20" s="3">
-        <v>0.50895833333333296</v>
-      </c>
-      <c r="E20" s="3"/>
+      <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
+      <c r="A21" s="20"/>
       <c r="B21" t="s">
         <v>18</v>
       </c>
@@ -1795,13 +1737,10 @@
         <f>VLOOKUP(B21, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E66</v>
       </c>
-      <c r="D21" s="3">
-        <v>0.55062500000000003</v>
-      </c>
-      <c r="E21" s="3"/>
+      <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="26"/>
+      <c r="A22" s="20"/>
       <c r="B22" t="s">
         <v>17</v>
       </c>
@@ -1809,13 +1748,10 @@
         <f>VLOOKUP(B22, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D22" s="3">
-        <v>0.59229166666666699</v>
-      </c>
-      <c r="E22" s="3"/>
+      <c r="E22" s="2"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="26"/>
+      <c r="A23" s="20"/>
       <c r="B23" t="s">
         <v>19</v>
       </c>
@@ -1823,13 +1759,10 @@
         <f>VLOOKUP(B23, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E62</v>
       </c>
-      <c r="D23" s="3">
-        <v>0.63395833333333296</v>
-      </c>
-      <c r="E23" s="3"/>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="26"/>
+      <c r="A24" s="20"/>
       <c r="B24" t="s">
         <v>12</v>
       </c>
@@ -1837,19 +1770,16 @@
         <f>VLOOKUP(B24, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E61</v>
       </c>
-      <c r="D24" s="3">
-        <v>0.67562500000000003</v>
-      </c>
-      <c r="E24" s="3"/>
+      <c r="E24" s="2"/>
       <c r="G24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J24" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="26"/>
+      <c r="A25" s="20"/>
       <c r="B25" t="s">
         <v>8</v>
       </c>
@@ -1857,19 +1787,16 @@
         <f>VLOOKUP(B25, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E47</v>
       </c>
-      <c r="D25" s="3">
-        <v>0.71729166666666699</v>
-      </c>
-      <c r="E25" s="3"/>
+      <c r="E25" s="2"/>
       <c r="G25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H25" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="26"/>
+      <c r="A26" s="20"/>
       <c r="B26" t="s">
         <v>12</v>
       </c>
@@ -1877,19 +1804,16 @@
         <f>VLOOKUP(B26, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E61</v>
       </c>
-      <c r="D26" s="3">
-        <v>0.75895833333333296</v>
-      </c>
-      <c r="E26" s="3"/>
+      <c r="E26" s="2"/>
       <c r="G26" t="s">
-        <v>271</v>
-      </c>
-      <c r="H26" s="23">
+        <v>270</v>
+      </c>
+      <c r="H26" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
+      <c r="A27" s="20"/>
       <c r="B27" t="s">
         <v>20</v>
       </c>
@@ -1897,33 +1821,27 @@
         <f>VLOOKUP(B27, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E95</v>
       </c>
-      <c r="D27" s="3">
-        <v>0.80062500000000003</v>
-      </c>
-      <c r="E27" s="3"/>
+      <c r="E27" s="2"/>
       <c r="G27" t="s">
-        <v>271</v>
-      </c>
-      <c r="H27" s="23" t="s">
-        <v>273</v>
+        <v>270</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="27"/>
-      <c r="B28" s="4" t="s">
+      <c r="A28" s="22"/>
+      <c r="B28" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C28" t="str">
         <f>VLOOKUP(B28, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D28" s="3">
-        <v>0.84229166666666699</v>
-      </c>
-      <c r="E28" s="3"/>
+      <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -1933,13 +1851,10 @@
         <f>VLOOKUP(B29, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E34</v>
       </c>
-      <c r="D29" s="3">
-        <v>0.88395833333333296</v>
-      </c>
-      <c r="E29" s="3"/>
+      <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
+      <c r="A30" s="20"/>
       <c r="B30" t="s">
         <v>8</v>
       </c>
@@ -1947,13 +1862,10 @@
         <f>VLOOKUP(B30, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E47</v>
       </c>
-      <c r="D30" s="3">
-        <v>0.92562500000000003</v>
-      </c>
-      <c r="E30" s="3"/>
+      <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="26"/>
+      <c r="A31" s="20"/>
       <c r="B31" t="s">
         <v>9</v>
       </c>
@@ -1961,13 +1873,10 @@
         <f>VLOOKUP(B31, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E7</v>
       </c>
-      <c r="D31" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E31" s="3"/>
+      <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
+      <c r="A32" s="20"/>
       <c r="B32" t="s">
         <v>23</v>
       </c>
@@ -1975,13 +1884,10 @@
         <f>VLOOKUP(B32, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E10</v>
       </c>
-      <c r="D32" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E32" s="3"/>
+      <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="26"/>
+      <c r="A33" s="20"/>
       <c r="B33" t="s">
         <v>17</v>
       </c>
@@ -1989,13 +1895,10 @@
         <f>VLOOKUP(B33, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D33" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E33" s="3"/>
+      <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="26"/>
+      <c r="A34" s="20"/>
       <c r="B34" t="s">
         <v>21</v>
       </c>
@@ -2003,13 +1906,10 @@
         <f>VLOOKUP(B34, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E90</v>
       </c>
-      <c r="D34" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E34" s="3"/>
+      <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="26"/>
+      <c r="A35" s="20"/>
       <c r="B35" t="s">
         <v>22</v>
       </c>
@@ -2017,13 +1917,10 @@
         <f>VLOOKUP(B35, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E33</v>
       </c>
-      <c r="D35" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E35" s="3"/>
+      <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="26"/>
+      <c r="A36" s="20"/>
       <c r="B36" t="s">
         <v>23</v>
       </c>
@@ -2031,13 +1928,10 @@
         <f>VLOOKUP(B36, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E10</v>
       </c>
-      <c r="D36" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E36" s="3"/>
+      <c r="E36" s="2"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="26"/>
+      <c r="A37" s="20"/>
       <c r="B37" t="s">
         <v>82</v>
       </c>
@@ -2045,11 +1939,10 @@
         <f>VLOOKUP(B37, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E17</v>
       </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
+      <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="26"/>
+      <c r="A38" s="20"/>
       <c r="B38" t="s">
         <v>123</v>
       </c>
@@ -2057,13 +1950,10 @@
         <f>VLOOKUP(B38, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E97</v>
       </c>
-      <c r="D38" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E38" s="3"/>
+      <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="26"/>
+      <c r="A39" s="20"/>
       <c r="B39" t="s">
         <v>20</v>
       </c>
@@ -2071,13 +1961,10 @@
         <f>VLOOKUP(B39, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E95</v>
       </c>
-      <c r="D39" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E39" s="3"/>
+      <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="26"/>
+      <c r="A40" s="20"/>
       <c r="B40" t="s">
         <v>17</v>
       </c>
@@ -2085,13 +1972,10 @@
         <f>VLOOKUP(B40, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D40" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E40" s="3"/>
+      <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="26"/>
+      <c r="A41" s="20"/>
       <c r="B41" t="s">
         <v>82</v>
       </c>
@@ -2099,13 +1983,10 @@
         <f>VLOOKUP(B41, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E17</v>
       </c>
-      <c r="D41" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E41" s="3"/>
+      <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="26"/>
+      <c r="A42" s="20"/>
       <c r="B42" t="s">
         <v>114</v>
       </c>
@@ -2113,11 +1994,10 @@
         <f>VLOOKUP(B42, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E75</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
+      <c r="E42" s="2"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="26"/>
+      <c r="A43" s="20"/>
       <c r="B43" t="s">
         <v>142</v>
       </c>
@@ -2125,13 +2005,10 @@
         <f>VLOOKUP(B43, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E28</v>
       </c>
-      <c r="D43" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E43" s="3"/>
+      <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="26"/>
+      <c r="A44" s="20"/>
       <c r="B44" t="s">
         <v>20</v>
       </c>
@@ -2139,13 +2016,10 @@
         <f>VLOOKUP(B44, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E95</v>
       </c>
-      <c r="D44" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E44" s="3"/>
+      <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="26"/>
+      <c r="A45" s="20"/>
       <c r="B45" t="s">
         <v>24</v>
       </c>
@@ -2153,27 +2027,21 @@
         <f>VLOOKUP(B45, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E91</v>
       </c>
-      <c r="D45" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E45" s="3"/>
+      <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="27"/>
-      <c r="B46" s="4" t="s">
+      <c r="A46" s="22"/>
+      <c r="B46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C46" t="str">
         <f>VLOOKUP(B46, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E10</v>
       </c>
-      <c r="D46" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E46" s="3"/>
+      <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="21" t="s">
         <v>86</v>
       </c>
       <c r="B47" t="s">
@@ -2183,13 +2051,10 @@
         <f>VLOOKUP(B47, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E34</v>
       </c>
-      <c r="D47" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E47" s="3"/>
+      <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="26"/>
+      <c r="A48" s="20"/>
       <c r="B48" t="s">
         <v>67</v>
       </c>
@@ -2197,13 +2062,10 @@
         <f>VLOOKUP(B48, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E29</v>
       </c>
-      <c r="D48" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E48" s="3"/>
+      <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="26"/>
+      <c r="A49" s="20"/>
       <c r="B49" t="s">
         <v>68</v>
       </c>
@@ -2211,13 +2073,10 @@
         <f>VLOOKUP(B49, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E39</v>
       </c>
-      <c r="D49" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E49" s="3"/>
+      <c r="E49" s="2"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="26"/>
+      <c r="A50" s="20"/>
       <c r="B50" t="s">
         <v>23</v>
       </c>
@@ -2225,13 +2084,10 @@
         <f>VLOOKUP(B50, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E10</v>
       </c>
-      <c r="D50" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E50" s="3"/>
+      <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="26"/>
+      <c r="A51" s="20"/>
       <c r="B51" t="s">
         <v>143</v>
       </c>
@@ -2239,13 +2095,10 @@
         <f>VLOOKUP(B51, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E83</v>
       </c>
-      <c r="D51" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E51" s="3"/>
+      <c r="E51" s="2"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="26"/>
+      <c r="A52" s="20"/>
       <c r="B52" t="s">
         <v>66</v>
       </c>
@@ -2253,13 +2106,10 @@
         <f>VLOOKUP(B52, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E34</v>
       </c>
-      <c r="D52" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E52" s="3"/>
+      <c r="E52" s="2"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="26"/>
+      <c r="A53" s="20"/>
       <c r="B53" t="s">
         <v>15</v>
       </c>
@@ -2267,13 +2117,10 @@
         <f>VLOOKUP(B53, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E33</v>
       </c>
-      <c r="D53" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E53" s="3"/>
+      <c r="E53" s="2"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="26"/>
+      <c r="A54" s="20"/>
       <c r="B54" t="s">
         <v>69</v>
       </c>
@@ -2281,13 +2128,10 @@
         <f>VLOOKUP(B54, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E86</v>
       </c>
-      <c r="D54" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E54" s="3"/>
+      <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="26"/>
+      <c r="A55" s="20"/>
       <c r="B55" t="s">
         <v>144</v>
       </c>
@@ -2295,13 +2139,10 @@
         <f>VLOOKUP(B55, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E8</v>
       </c>
-      <c r="D55" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E55" s="3"/>
+      <c r="E55" s="2"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="26"/>
+      <c r="A56" s="20"/>
       <c r="B56" t="s">
         <v>143</v>
       </c>
@@ -2309,13 +2150,10 @@
         <f>VLOOKUP(B56, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E83</v>
       </c>
-      <c r="D56" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E56" s="3"/>
+      <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="26"/>
+      <c r="A57" s="20"/>
       <c r="B57" t="s">
         <v>70</v>
       </c>
@@ -2323,13 +2161,10 @@
         <f>VLOOKUP(B57, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E71</v>
       </c>
-      <c r="D57" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E57" s="3"/>
+      <c r="E57" s="2"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="26"/>
+      <c r="A58" s="20"/>
       <c r="B58" t="s">
         <v>71</v>
       </c>
@@ -2337,13 +2172,10 @@
         <f>VLOOKUP(B58, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E70</v>
       </c>
-      <c r="D58" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E58" s="3"/>
+      <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="26"/>
+      <c r="A59" s="20"/>
       <c r="B59" t="s">
         <v>72</v>
       </c>
@@ -2351,13 +2183,10 @@
         <f>VLOOKUP(B59, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E72</v>
       </c>
-      <c r="D59" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E59" s="3"/>
+      <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="26"/>
+      <c r="A60" s="20"/>
       <c r="B60" t="s">
         <v>66</v>
       </c>
@@ -2365,13 +2194,10 @@
         <f>VLOOKUP(B60, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E34</v>
       </c>
-      <c r="D60" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E60" s="3"/>
+      <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="26"/>
+      <c r="A61" s="20"/>
       <c r="B61" t="s">
         <v>73</v>
       </c>
@@ -2379,13 +2205,10 @@
         <f>VLOOKUP(B61, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E32</v>
       </c>
-      <c r="D61" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E61" s="3"/>
+      <c r="E61" s="2"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="26"/>
+      <c r="A62" s="20"/>
       <c r="B62" t="s">
         <v>67</v>
       </c>
@@ -2393,13 +2216,10 @@
         <f>VLOOKUP(B62, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E29</v>
       </c>
-      <c r="D62" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E62" s="3"/>
+      <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="26"/>
+      <c r="A63" s="20"/>
       <c r="B63" t="s">
         <v>74</v>
       </c>
@@ -2407,13 +2227,10 @@
         <f>VLOOKUP(B63, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E58</v>
       </c>
-      <c r="D63" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E63" s="3"/>
+      <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="26"/>
+      <c r="A64" s="20"/>
       <c r="B64" t="s">
         <v>75</v>
       </c>
@@ -2421,13 +2238,10 @@
         <f>VLOOKUP(B64, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E59</v>
       </c>
-      <c r="D64" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E64" s="3"/>
+      <c r="E64" s="2"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="26"/>
+      <c r="A65" s="20"/>
       <c r="B65" t="s">
         <v>76</v>
       </c>
@@ -2435,13 +2249,10 @@
         <f>VLOOKUP(B65, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D65" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E65" s="3"/>
+      <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="26"/>
+      <c r="A66" s="20"/>
       <c r="B66" t="s">
         <v>114</v>
       </c>
@@ -2449,13 +2260,10 @@
         <f>VLOOKUP(B66, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E75</v>
       </c>
-      <c r="D66" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E66" s="3"/>
+      <c r="E66" s="2"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="26"/>
+      <c r="A67" s="20"/>
       <c r="B67" t="s">
         <v>77</v>
       </c>
@@ -2463,13 +2271,10 @@
         <f>VLOOKUP(B67, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E38</v>
       </c>
-      <c r="D67" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E67" s="3"/>
+      <c r="E67" s="2"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="26" t="s">
+      <c r="A68" s="20" t="s">
         <v>87</v>
       </c>
       <c r="B68" t="s">
@@ -2479,13 +2284,10 @@
         <f>VLOOKUP(B68, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E62</v>
       </c>
-      <c r="D68" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E68" s="3"/>
+      <c r="E68" s="2"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="26"/>
+      <c r="A69" s="20"/>
       <c r="B69" t="s">
         <v>78</v>
       </c>
@@ -2493,13 +2295,10 @@
         <f>VLOOKUP(B69, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E55</v>
       </c>
-      <c r="D69" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E69" s="3"/>
+      <c r="E69" s="2"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="26"/>
+      <c r="A70" s="20"/>
       <c r="B70" t="s">
         <v>9</v>
       </c>
@@ -2507,13 +2306,10 @@
         <f>VLOOKUP(B70, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E7</v>
       </c>
-      <c r="D70" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E70" s="3"/>
+      <c r="E70" s="2"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="26"/>
+      <c r="A71" s="20"/>
       <c r="B71" t="s">
         <v>145</v>
       </c>
@@ -2521,13 +2317,10 @@
         <f>VLOOKUP(B71, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E27</v>
       </c>
-      <c r="D71" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E71" s="3"/>
+      <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="26"/>
+      <c r="A72" s="20"/>
       <c r="B72" t="s">
         <v>146</v>
       </c>
@@ -2535,13 +2328,10 @@
         <f>VLOOKUP(B72, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E41</v>
       </c>
-      <c r="D72" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E72" s="3"/>
+      <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="26"/>
+      <c r="A73" s="20"/>
       <c r="B73" t="s">
         <v>113</v>
       </c>
@@ -2549,13 +2339,10 @@
         <f>VLOOKUP(B73, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E74</v>
       </c>
-      <c r="D73" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E73" s="3"/>
+      <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="26"/>
+      <c r="A74" s="20"/>
       <c r="B74" t="s">
         <v>114</v>
       </c>
@@ -2563,13 +2350,10 @@
         <f>VLOOKUP(B74, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E75</v>
       </c>
-      <c r="D74" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E74" s="3"/>
+      <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="26"/>
+      <c r="A75" s="20"/>
       <c r="B75" t="s">
         <v>19</v>
       </c>
@@ -2577,13 +2361,10 @@
         <f>VLOOKUP(B75, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E62</v>
       </c>
-      <c r="D75" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E75" s="3"/>
+      <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="26"/>
+      <c r="A76" s="20"/>
       <c r="B76" t="s">
         <v>114</v>
       </c>
@@ -2591,13 +2372,10 @@
         <f>VLOOKUP(B76, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E75</v>
       </c>
-      <c r="D76" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E76" s="3"/>
+      <c r="E76" s="2"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="26"/>
+      <c r="A77" s="20"/>
       <c r="B77" t="s">
         <v>7</v>
       </c>
@@ -2605,13 +2383,10 @@
         <f>VLOOKUP(B77, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D77" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E77" s="3"/>
+      <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="26"/>
+      <c r="A78" s="20"/>
       <c r="B78" t="s">
         <v>80</v>
       </c>
@@ -2619,13 +2394,10 @@
         <f>VLOOKUP(B78, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E87</v>
       </c>
-      <c r="D78" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E78" s="3"/>
+      <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="26"/>
+      <c r="A79" s="20"/>
       <c r="B79" t="s">
         <v>79</v>
       </c>
@@ -2633,13 +2405,10 @@
         <f>VLOOKUP(B79, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E76</v>
       </c>
-      <c r="D79" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E79" s="3"/>
+      <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="26"/>
+      <c r="A80" s="20"/>
       <c r="B80" t="s">
         <v>147</v>
       </c>
@@ -2647,13 +2416,10 @@
         <f>VLOOKUP(B80, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E9</v>
       </c>
-      <c r="D80" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E80" s="3"/>
+      <c r="E80" s="2"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="26"/>
+      <c r="A81" s="20"/>
       <c r="B81" t="s">
         <v>19</v>
       </c>
@@ -2661,13 +2427,10 @@
         <f>VLOOKUP(B81, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E62</v>
       </c>
-      <c r="D81" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E81" s="3"/>
+      <c r="E81" s="2"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="26"/>
+      <c r="A82" s="20"/>
       <c r="B82" t="s">
         <v>81</v>
       </c>
@@ -2675,13 +2438,10 @@
         <f>VLOOKUP(B82, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E51</v>
       </c>
-      <c r="D82" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E82" s="3"/>
+      <c r="E82" s="2"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="26"/>
+      <c r="A83" s="20"/>
       <c r="B83" t="s">
         <v>76</v>
       </c>
@@ -2689,13 +2449,10 @@
         <f>VLOOKUP(B83, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D83" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E83" s="3"/>
+      <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="26"/>
+      <c r="A84" s="20"/>
       <c r="B84" t="s">
         <v>82</v>
       </c>
@@ -2703,13 +2460,10 @@
         <f>VLOOKUP(B84, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E17</v>
       </c>
-      <c r="D84" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E84" s="3"/>
+      <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="26"/>
+      <c r="A85" s="20"/>
       <c r="B85" t="s">
         <v>83</v>
       </c>
@@ -2717,13 +2471,10 @@
         <f>VLOOKUP(B85, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E21</v>
       </c>
-      <c r="D85" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E85" s="3"/>
+      <c r="E85" s="2"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="26"/>
+      <c r="A86" s="20"/>
       <c r="B86" t="s">
         <v>84</v>
       </c>
@@ -2731,13 +2482,10 @@
         <f>VLOOKUP(B86, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E16</v>
       </c>
-      <c r="D86" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E86" s="3"/>
+      <c r="E86" s="2"/>
     </row>
     <row r="87" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="26" t="s">
+      <c r="A87" s="20" t="s">
         <v>91</v>
       </c>
       <c r="B87" t="s">
@@ -2747,13 +2495,10 @@
         <f>VLOOKUP(B87, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E3</v>
       </c>
-      <c r="D87" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E87" s="3"/>
+      <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="26"/>
+      <c r="A88" s="20"/>
       <c r="B88" t="s">
         <v>7</v>
       </c>
@@ -2761,13 +2506,10 @@
         <f>VLOOKUP(B88, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D88" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E88" s="3"/>
+      <c r="E88" s="2"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="26"/>
+      <c r="A89" s="20"/>
       <c r="B89" t="s">
         <v>143</v>
       </c>
@@ -2775,13 +2517,10 @@
         <f>VLOOKUP(B89, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E83</v>
       </c>
-      <c r="D89" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E89" s="3"/>
+      <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="26"/>
+      <c r="A90" s="20"/>
       <c r="B90" t="s">
         <v>148</v>
       </c>
@@ -2789,13 +2528,10 @@
         <f>VLOOKUP(B90, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E84</v>
       </c>
-      <c r="D90" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E90" s="3"/>
+      <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="26"/>
+      <c r="A91" s="20"/>
       <c r="B91" t="s">
         <v>88</v>
       </c>
@@ -2803,13 +2539,10 @@
         <f>VLOOKUP(B91, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E24</v>
       </c>
-      <c r="D91" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E91" s="3"/>
+      <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="26"/>
+      <c r="A92" s="20"/>
       <c r="B92" t="s">
         <v>143</v>
       </c>
@@ -2817,13 +2550,10 @@
         <f>VLOOKUP(B92, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E83</v>
       </c>
-      <c r="D92" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E92" s="3"/>
+      <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="26"/>
+      <c r="A93" s="20"/>
       <c r="B93" t="s">
         <v>89</v>
       </c>
@@ -2831,13 +2561,10 @@
         <f>VLOOKUP(B93, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E25</v>
       </c>
-      <c r="D93" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E93" s="3"/>
+      <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="26"/>
+      <c r="A94" s="20"/>
       <c r="B94" t="s">
         <v>143</v>
       </c>
@@ -2845,13 +2572,10 @@
         <f>VLOOKUP(B94, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E83</v>
       </c>
-      <c r="D94" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E94" s="3"/>
+      <c r="E94" s="2"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="26"/>
+      <c r="A95" s="20"/>
       <c r="B95" t="s">
         <v>70</v>
       </c>
@@ -2859,13 +2583,10 @@
         <f>VLOOKUP(B95, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E71</v>
       </c>
-      <c r="D95" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E95" s="3"/>
+      <c r="E95" s="2"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="26"/>
+      <c r="A96" s="20"/>
       <c r="B96" t="s">
         <v>90</v>
       </c>
@@ -2873,13 +2594,10 @@
         <f>VLOOKUP(B96, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E4</v>
       </c>
-      <c r="D96" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E96" s="3"/>
+      <c r="E96" s="2"/>
     </row>
     <row r="97" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="26" t="s">
+      <c r="A97" s="20" t="s">
         <v>99</v>
       </c>
       <c r="B97" t="s">
@@ -2889,13 +2607,10 @@
         <f>VLOOKUP(B97, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E5</v>
       </c>
-      <c r="D97" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E97" s="3"/>
+      <c r="E97" s="2"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="26"/>
+      <c r="A98" s="20"/>
       <c r="B98" t="s">
         <v>67</v>
       </c>
@@ -2903,13 +2618,10 @@
         <f>VLOOKUP(B98, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E29</v>
       </c>
-      <c r="D98" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E98" s="3"/>
+      <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="26"/>
+      <c r="A99" s="20"/>
       <c r="B99" t="s">
         <v>76</v>
       </c>
@@ -2917,13 +2629,10 @@
         <f>VLOOKUP(B99, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D99" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E99" s="3"/>
+      <c r="E99" s="2"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="26"/>
+      <c r="A100" s="20"/>
       <c r="B100" t="s">
         <v>143</v>
       </c>
@@ -2931,13 +2640,10 @@
         <f>VLOOKUP(B100, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E83</v>
       </c>
-      <c r="D100" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E100" s="3"/>
+      <c r="E100" s="2"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="26"/>
+      <c r="A101" s="20"/>
       <c r="B101" t="s">
         <v>8</v>
       </c>
@@ -2945,13 +2651,10 @@
         <f>VLOOKUP(B101, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E47</v>
       </c>
-      <c r="D101" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E101" s="3"/>
+      <c r="E101" s="2"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="26"/>
+      <c r="A102" s="20"/>
       <c r="B102" t="s">
         <v>93</v>
       </c>
@@ -2959,13 +2662,10 @@
         <f>VLOOKUP(B102, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E53</v>
       </c>
-      <c r="D102" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E102" s="3"/>
+      <c r="E102" s="2"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="26"/>
+      <c r="A103" s="20"/>
       <c r="B103" t="s">
         <v>92</v>
       </c>
@@ -2973,13 +2673,10 @@
         <f>VLOOKUP(B103, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E5</v>
       </c>
-      <c r="D103" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E103" s="3"/>
+      <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="26"/>
+      <c r="A104" s="20"/>
       <c r="B104" t="s">
         <v>23</v>
       </c>
@@ -2987,13 +2684,10 @@
         <f>VLOOKUP(B104, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E10</v>
       </c>
-      <c r="D104" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E104" s="3"/>
+      <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="26"/>
+      <c r="A105" s="20"/>
       <c r="B105" t="s">
         <v>149</v>
       </c>
@@ -3001,13 +2695,10 @@
         <f>VLOOKUP(B105, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E40</v>
       </c>
-      <c r="D105" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E105" s="3"/>
+      <c r="E105" s="2"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="26"/>
+      <c r="A106" s="20"/>
       <c r="B106" t="s">
         <v>150</v>
       </c>
@@ -3015,13 +2706,10 @@
         <f>VLOOKUP(B106, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E11</v>
       </c>
-      <c r="D106" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E106" s="3"/>
+      <c r="E106" s="2"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="26"/>
+      <c r="A107" s="20"/>
       <c r="B107" t="s">
         <v>94</v>
       </c>
@@ -3029,13 +2717,10 @@
         <f>VLOOKUP(B107, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E49</v>
       </c>
-      <c r="D107" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E107" s="3"/>
+      <c r="E107" s="2"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="26"/>
+      <c r="A108" s="20"/>
       <c r="B108" t="s">
         <v>95</v>
       </c>
@@ -3043,13 +2728,10 @@
         <f>VLOOKUP(B108, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E1</v>
       </c>
-      <c r="D108" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E108" s="3"/>
+      <c r="E108" s="2"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="26"/>
+      <c r="A109" s="20"/>
       <c r="B109" t="s">
         <v>151</v>
       </c>
@@ -3057,13 +2739,10 @@
         <f>VLOOKUP(B109, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E6</v>
       </c>
-      <c r="D109" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E109" s="3"/>
+      <c r="E109" s="2"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="26"/>
+      <c r="A110" s="20"/>
       <c r="B110" t="s">
         <v>96</v>
       </c>
@@ -3071,13 +2750,10 @@
         <f>VLOOKUP(B110, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E37</v>
       </c>
-      <c r="D110" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E110" s="3"/>
+      <c r="E110" s="2"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="26"/>
+      <c r="A111" s="20"/>
       <c r="B111" t="s">
         <v>97</v>
       </c>
@@ -3085,13 +2761,10 @@
         <f>VLOOKUP(B111, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E54</v>
       </c>
-      <c r="D111" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E111" s="3"/>
+      <c r="E111" s="2"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="26"/>
+      <c r="A112" s="20"/>
       <c r="B112" t="s">
         <v>152</v>
       </c>
@@ -3099,13 +2772,10 @@
         <f>VLOOKUP(B112, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E12</v>
       </c>
-      <c r="D112" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E112" s="3"/>
+      <c r="E112" s="2"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="26"/>
+      <c r="A113" s="20"/>
       <c r="B113" t="s">
         <v>98</v>
       </c>
@@ -3113,13 +2783,10 @@
         <f>VLOOKUP(B113, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E2</v>
       </c>
-      <c r="D113" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E113" s="3"/>
+      <c r="E113" s="2"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="26"/>
+      <c r="A114" s="20"/>
       <c r="B114" t="s">
         <v>76</v>
       </c>
@@ -3127,13 +2794,10 @@
         <f>VLOOKUP(B114, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D114" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E114" s="3"/>
+      <c r="E114" s="2"/>
     </row>
     <row r="115" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="20" t="s">
         <v>109</v>
       </c>
       <c r="B115" t="s">
@@ -3143,13 +2807,10 @@
         <f>VLOOKUP(B115, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E55</v>
       </c>
-      <c r="D115" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E115" s="3"/>
+      <c r="E115" s="2"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" s="26"/>
+      <c r="A116" s="20"/>
       <c r="B116" t="s">
         <v>8</v>
       </c>
@@ -3157,13 +2818,10 @@
         <f>VLOOKUP(B116, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E47</v>
       </c>
-      <c r="D116" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E116" s="3"/>
+      <c r="E116" s="2"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="26"/>
+      <c r="A117" s="20"/>
       <c r="B117" t="s">
         <v>100</v>
       </c>
@@ -3171,13 +2829,10 @@
         <f>VLOOKUP(B117, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E56</v>
       </c>
-      <c r="D117" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E117" s="3"/>
+      <c r="E117" s="2"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="26"/>
+      <c r="A118" s="20"/>
       <c r="B118" t="s">
         <v>19</v>
       </c>
@@ -3185,13 +2840,10 @@
         <f>VLOOKUP(B118, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E62</v>
       </c>
-      <c r="D118" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E118" s="3"/>
+      <c r="E118" s="2"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="26"/>
+      <c r="A119" s="20"/>
       <c r="B119" t="s">
         <v>12</v>
       </c>
@@ -3199,13 +2851,10 @@
         <f>VLOOKUP(B119, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E61</v>
       </c>
-      <c r="D119" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E119" s="3"/>
+      <c r="E119" s="2"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="26"/>
+      <c r="A120" s="20"/>
       <c r="B120" t="s">
         <v>101</v>
       </c>
@@ -3213,13 +2862,10 @@
         <f>VLOOKUP(B120, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E92</v>
       </c>
-      <c r="D120" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E120" s="3"/>
+      <c r="E120" s="2"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="26"/>
+      <c r="A121" s="20"/>
       <c r="B121" t="s">
         <v>12</v>
       </c>
@@ -3227,13 +2873,10 @@
         <f>VLOOKUP(B121, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E61</v>
       </c>
-      <c r="D121" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E121" s="3"/>
+      <c r="E121" s="2"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="26"/>
+      <c r="A122" s="20"/>
       <c r="B122" t="s">
         <v>17</v>
       </c>
@@ -3241,13 +2884,10 @@
         <f>VLOOKUP(B122, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D122" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E122" s="3"/>
+      <c r="E122" s="2"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="26"/>
+      <c r="A123" s="20"/>
       <c r="B123" t="s">
         <v>82</v>
       </c>
@@ -3255,13 +2895,10 @@
         <f>VLOOKUP(B123, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E17</v>
       </c>
-      <c r="D123" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E123" s="3"/>
+      <c r="E123" s="2"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="26"/>
+      <c r="A124" s="20"/>
       <c r="B124" t="s">
         <v>102</v>
       </c>
@@ -3269,13 +2906,10 @@
         <f>VLOOKUP(B124, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E18</v>
       </c>
-      <c r="D124" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E124" s="3"/>
+      <c r="E124" s="2"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="26"/>
+      <c r="A125" s="20"/>
       <c r="B125" t="s">
         <v>94</v>
       </c>
@@ -3283,13 +2917,10 @@
         <f>VLOOKUP(B125, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E49</v>
       </c>
-      <c r="D125" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E125" s="3"/>
+      <c r="E125" s="2"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="26"/>
+      <c r="A126" s="20"/>
       <c r="B126" t="s">
         <v>22</v>
       </c>
@@ -3297,13 +2928,10 @@
         <f>VLOOKUP(B126, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E33</v>
       </c>
-      <c r="D126" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E126" s="3"/>
+      <c r="E126" s="2"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="26"/>
+      <c r="A127" s="20"/>
       <c r="B127" t="s">
         <v>103</v>
       </c>
@@ -3311,13 +2939,10 @@
         <f>VLOOKUP(B127, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E23</v>
       </c>
-      <c r="D127" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E127" s="3"/>
+      <c r="E127" s="2"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="26"/>
+      <c r="A128" s="20"/>
       <c r="B128" t="s">
         <v>104</v>
       </c>
@@ -3325,13 +2950,10 @@
         <f>VLOOKUP(B128, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E22</v>
       </c>
-      <c r="D128" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E128" s="3"/>
+      <c r="E128" s="2"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="26"/>
+      <c r="A129" s="20"/>
       <c r="B129" t="s">
         <v>70</v>
       </c>
@@ -3339,13 +2961,10 @@
         <f>VLOOKUP(B129, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E71</v>
       </c>
-      <c r="D129" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E129" s="3"/>
+      <c r="E129" s="2"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="26"/>
+      <c r="A130" s="20"/>
       <c r="B130" t="s">
         <v>93</v>
       </c>
@@ -3353,13 +2972,10 @@
         <f>VLOOKUP(B130, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E53</v>
       </c>
-      <c r="D130" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E130" s="3"/>
+      <c r="E130" s="2"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="26"/>
+      <c r="A131" s="20"/>
       <c r="B131" t="s">
         <v>71</v>
       </c>
@@ -3367,13 +2983,10 @@
         <f>VLOOKUP(B131, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E70</v>
       </c>
-      <c r="D131" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E131" s="3"/>
+      <c r="E131" s="2"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="26"/>
+      <c r="A132" s="20"/>
       <c r="B132" t="s">
         <v>105</v>
       </c>
@@ -3381,13 +2994,10 @@
         <f>VLOOKUP(B132, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E73</v>
       </c>
-      <c r="D132" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E132" s="3"/>
+      <c r="E132" s="2"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133" s="26"/>
+      <c r="A133" s="20"/>
       <c r="B133" t="s">
         <v>96</v>
       </c>
@@ -3395,13 +3005,10 @@
         <f>VLOOKUP(B133, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E37</v>
       </c>
-      <c r="D133" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E133" s="3"/>
+      <c r="E133" s="2"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" s="26"/>
+      <c r="A134" s="20"/>
       <c r="B134" t="s">
         <v>77</v>
       </c>
@@ -3409,13 +3016,10 @@
         <f>VLOOKUP(B134, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E38</v>
       </c>
-      <c r="D134" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E134" s="3"/>
+      <c r="E134" s="2"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" s="26"/>
+      <c r="A135" s="20"/>
       <c r="B135" t="s">
         <v>22</v>
       </c>
@@ -3423,13 +3027,10 @@
         <f>VLOOKUP(B135, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E33</v>
       </c>
-      <c r="D135" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E135" s="3"/>
+      <c r="E135" s="2"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A136" s="26"/>
+      <c r="A136" s="20"/>
       <c r="B136" t="s">
         <v>70</v>
       </c>
@@ -3437,13 +3038,10 @@
         <f>VLOOKUP(B136, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E71</v>
       </c>
-      <c r="D136" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E136" s="3"/>
+      <c r="E136" s="2"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A137" s="26"/>
+      <c r="A137" s="20"/>
       <c r="B137" t="s">
         <v>71</v>
       </c>
@@ -3451,13 +3049,10 @@
         <f>VLOOKUP(B137, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E70</v>
       </c>
-      <c r="D137" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E137" s="3"/>
+      <c r="E137" s="2"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" s="26"/>
+      <c r="A138" s="20"/>
       <c r="B138" t="s">
         <v>106</v>
       </c>
@@ -3465,13 +3060,10 @@
         <f>VLOOKUP(B138, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E44</v>
       </c>
-      <c r="D138" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E138" s="3"/>
+      <c r="E138" s="2"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" s="26"/>
+      <c r="A139" s="20"/>
       <c r="B139" t="s">
         <v>107</v>
       </c>
@@ -3479,13 +3071,10 @@
         <f>VLOOKUP(B139, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E69</v>
       </c>
-      <c r="D139" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E139" s="3"/>
+      <c r="E139" s="2"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" s="26"/>
+      <c r="A140" s="20"/>
       <c r="B140" t="s">
         <v>76</v>
       </c>
@@ -3493,13 +3082,10 @@
         <f>VLOOKUP(B140, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D140" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E140" s="3"/>
+      <c r="E140" s="2"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" s="26"/>
+      <c r="A141" s="20"/>
       <c r="B141" t="s">
         <v>77</v>
       </c>
@@ -3507,13 +3093,10 @@
         <f>VLOOKUP(B141, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E38</v>
       </c>
-      <c r="D141" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E141" s="3"/>
+      <c r="E141" s="2"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" s="26"/>
+      <c r="A142" s="20"/>
       <c r="B142" t="s">
         <v>78</v>
       </c>
@@ -3521,13 +3104,10 @@
         <f>VLOOKUP(B142, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E55</v>
       </c>
-      <c r="D142" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E142" s="3"/>
+      <c r="E142" s="2"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" s="26"/>
+      <c r="A143" s="20"/>
       <c r="B143" t="s">
         <v>7</v>
       </c>
@@ -3535,13 +3115,10 @@
         <f>VLOOKUP(B143, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D143" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E143" s="3"/>
+      <c r="E143" s="2"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144" s="26"/>
+      <c r="A144" s="20"/>
       <c r="B144" t="s">
         <v>82</v>
       </c>
@@ -3549,13 +3126,10 @@
         <f>VLOOKUP(B144, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E17</v>
       </c>
-      <c r="D144" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E144" s="3"/>
+      <c r="E144" s="2"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="26"/>
+      <c r="A145" s="20"/>
       <c r="B145" t="s">
         <v>19</v>
       </c>
@@ -3563,13 +3137,10 @@
         <f>VLOOKUP(B145, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E62</v>
       </c>
-      <c r="D145" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E145" s="3"/>
+      <c r="E145" s="2"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" s="26"/>
+      <c r="A146" s="20"/>
       <c r="B146" t="s">
         <v>108</v>
       </c>
@@ -3577,13 +3148,10 @@
         <f>VLOOKUP(B146, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E68</v>
       </c>
-      <c r="D146" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E146" s="3"/>
+      <c r="E146" s="2"/>
     </row>
     <row r="147" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="26" t="s">
+      <c r="A147" s="20" t="s">
         <v>120</v>
       </c>
       <c r="B147" t="s">
@@ -3593,13 +3161,10 @@
         <f>VLOOKUP(B147, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E55</v>
       </c>
-      <c r="D147" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E147" s="3"/>
+      <c r="E147" s="2"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A148" s="26"/>
+      <c r="A148" s="20"/>
       <c r="B148" t="s">
         <v>7</v>
       </c>
@@ -3607,13 +3172,10 @@
         <f>VLOOKUP(B148, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D148" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E148" s="3"/>
+      <c r="E148" s="2"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A149" s="26"/>
+      <c r="A149" s="20"/>
       <c r="B149" t="s">
         <v>110</v>
       </c>
@@ -3621,13 +3183,10 @@
         <f>VLOOKUP(B149, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E98</v>
       </c>
-      <c r="D149" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E149" s="3"/>
+      <c r="E149" s="2"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A150" s="26"/>
+      <c r="A150" s="20"/>
       <c r="B150" t="s">
         <v>8</v>
       </c>
@@ -3635,13 +3194,10 @@
         <f>VLOOKUP(B150, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E47</v>
       </c>
-      <c r="D150" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E150" s="3"/>
+      <c r="E150" s="2"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A151" s="26"/>
+      <c r="A151" s="20"/>
       <c r="B151" t="s">
         <v>111</v>
       </c>
@@ -3649,13 +3205,10 @@
         <f>VLOOKUP(B151, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E45</v>
       </c>
-      <c r="D151" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E151" s="3"/>
+      <c r="E151" s="2"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A152" s="26"/>
+      <c r="A152" s="20"/>
       <c r="B152" t="s">
         <v>112</v>
       </c>
@@ -3663,13 +3216,10 @@
         <f>VLOOKUP(B152, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E36</v>
       </c>
-      <c r="D152" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E152" s="3"/>
+      <c r="E152" s="2"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A153" s="26"/>
+      <c r="A153" s="20"/>
       <c r="B153" t="s">
         <v>113</v>
       </c>
@@ -3677,13 +3227,10 @@
         <f>VLOOKUP(B153, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E74</v>
       </c>
-      <c r="D153" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E153" s="3"/>
+      <c r="E153" s="2"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A154" s="26"/>
+      <c r="A154" s="20"/>
       <c r="B154" t="s">
         <v>114</v>
       </c>
@@ -3691,13 +3238,10 @@
         <f>VLOOKUP(B154, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E75</v>
       </c>
-      <c r="D154" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E154" s="3"/>
+      <c r="E154" s="2"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A155" s="26"/>
+      <c r="A155" s="20"/>
       <c r="B155" t="s">
         <v>67</v>
       </c>
@@ -3705,13 +3249,10 @@
         <f>VLOOKUP(B155, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E29</v>
       </c>
-      <c r="D155" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E155" s="3"/>
+      <c r="E155" s="2"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A156" s="26"/>
+      <c r="A156" s="20"/>
       <c r="B156" t="s">
         <v>107</v>
       </c>
@@ -3719,13 +3260,10 @@
         <f>VLOOKUP(B156, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E69</v>
       </c>
-      <c r="D156" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E156" s="3"/>
+      <c r="E156" s="2"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A157" s="26"/>
+      <c r="A157" s="20"/>
       <c r="B157" t="s">
         <v>153</v>
       </c>
@@ -3733,13 +3271,10 @@
         <f>VLOOKUP(B157, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E14</v>
       </c>
-      <c r="D157" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E157" s="3"/>
+      <c r="E157" s="2"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A158" s="26"/>
+      <c r="A158" s="20"/>
       <c r="B158" t="s">
         <v>115</v>
       </c>
@@ -3747,13 +3282,10 @@
         <f>VLOOKUP(B158, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E35</v>
       </c>
-      <c r="D158" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E158" s="3"/>
+      <c r="E158" s="2"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A159" s="26"/>
+      <c r="A159" s="20"/>
       <c r="B159" t="s">
         <v>116</v>
       </c>
@@ -3761,13 +3293,10 @@
         <f>VLOOKUP(B159, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E46</v>
       </c>
-      <c r="D159" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E159" s="3"/>
+      <c r="E159" s="2"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A160" s="26"/>
+      <c r="A160" s="20"/>
       <c r="B160" t="s">
         <v>82</v>
       </c>
@@ -3775,13 +3304,10 @@
         <f>VLOOKUP(B160, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E17</v>
       </c>
-      <c r="D160" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E160" s="3"/>
+      <c r="E160" s="2"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A161" s="26"/>
+      <c r="A161" s="20"/>
       <c r="B161" t="s">
         <v>117</v>
       </c>
@@ -3789,13 +3315,10 @@
         <f>VLOOKUP(B161, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E30</v>
       </c>
-      <c r="D161" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E161" s="3"/>
+      <c r="E161" s="2"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A162" s="26"/>
+      <c r="A162" s="20"/>
       <c r="B162" t="s">
         <v>7</v>
       </c>
@@ -3803,13 +3326,10 @@
         <f>VLOOKUP(B162, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D162" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E162" s="3"/>
+      <c r="E162" s="2"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A163" s="26"/>
+      <c r="A163" s="20"/>
       <c r="B163" t="s">
         <v>118</v>
       </c>
@@ -3817,13 +3337,10 @@
         <f>VLOOKUP(B163, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E94</v>
       </c>
-      <c r="D163" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E163" s="3"/>
+      <c r="E163" s="2"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A164" s="26"/>
+      <c r="A164" s="20"/>
       <c r="B164" t="s">
         <v>119</v>
       </c>
@@ -3831,13 +3348,10 @@
         <f>VLOOKUP(B164, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E88</v>
       </c>
-      <c r="D164" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E164" s="3"/>
+      <c r="E164" s="2"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A165" s="26"/>
+      <c r="A165" s="20"/>
       <c r="B165" t="s">
         <v>9</v>
       </c>
@@ -3845,13 +3359,10 @@
         <f>VLOOKUP(B165, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E7</v>
       </c>
-      <c r="D165" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E165" s="3"/>
+      <c r="E165" s="2"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A166" s="26" t="s">
+      <c r="A166" s="20" t="s">
         <v>121</v>
       </c>
       <c r="B166" t="s">
@@ -3861,13 +3372,10 @@
         <f>VLOOKUP(B166, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E81</v>
       </c>
-      <c r="D166" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E166" s="3"/>
+      <c r="E166" s="2"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A167" s="26"/>
+      <c r="A167" s="20"/>
       <c r="B167" t="s">
         <v>7</v>
       </c>
@@ -3875,13 +3383,10 @@
         <f>VLOOKUP(B167, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D167" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E167" s="3"/>
+      <c r="E167" s="2"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A168" s="26"/>
+      <c r="A168" s="20"/>
       <c r="B168" t="s">
         <v>123</v>
       </c>
@@ -3889,13 +3394,10 @@
         <f>VLOOKUP(B168, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E97</v>
       </c>
-      <c r="D168" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E168" s="3"/>
+      <c r="E168" s="2"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A169" s="26"/>
+      <c r="A169" s="20"/>
       <c r="B169" t="s">
         <v>124</v>
       </c>
@@ -3903,13 +3405,10 @@
         <f>VLOOKUP(B169, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E99</v>
       </c>
-      <c r="D169" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E169" s="3"/>
+      <c r="E169" s="2"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A170" s="26"/>
+      <c r="A170" s="20"/>
       <c r="B170" t="s">
         <v>125</v>
       </c>
@@ -3917,13 +3416,10 @@
         <f>VLOOKUP(B170, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E26</v>
       </c>
-      <c r="D170" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E170" s="3"/>
+      <c r="E170" s="2"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A171" s="26"/>
+      <c r="A171" s="20"/>
       <c r="B171" t="s">
         <v>7</v>
       </c>
@@ -3931,13 +3427,10 @@
         <f>VLOOKUP(B171, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D171" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E171" s="3"/>
+      <c r="E171" s="2"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172" s="26"/>
+      <c r="A172" s="20"/>
       <c r="B172" t="s">
         <v>126</v>
       </c>
@@ -3945,13 +3438,10 @@
         <f>VLOOKUP(B172, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E93</v>
       </c>
-      <c r="D172" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E172" s="3"/>
+      <c r="E172" s="2"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A173" s="26"/>
+      <c r="A173" s="20"/>
       <c r="B173" t="s">
         <v>7</v>
       </c>
@@ -3959,13 +3449,10 @@
         <f>VLOOKUP(B173, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D173" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E173" s="3"/>
+      <c r="E173" s="2"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174" s="26"/>
+      <c r="A174" s="20"/>
       <c r="B174" t="s">
         <v>8</v>
       </c>
@@ -3973,13 +3460,10 @@
         <f>VLOOKUP(B174, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E47</v>
       </c>
-      <c r="D174" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E174" s="3"/>
+      <c r="E174" s="2"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175" s="26"/>
+      <c r="A175" s="20"/>
       <c r="B175" t="s">
         <v>7</v>
       </c>
@@ -3987,13 +3471,10 @@
         <f>VLOOKUP(B175, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D175" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E175" s="3"/>
+      <c r="E175" s="2"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176" s="26"/>
+      <c r="A176" s="20"/>
       <c r="B176" t="s">
         <v>8</v>
       </c>
@@ -4001,13 +3482,10 @@
         <f>VLOOKUP(B176, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E47</v>
       </c>
-      <c r="D176" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E176" s="3"/>
+      <c r="E176" s="2"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177" s="26"/>
+      <c r="A177" s="20"/>
       <c r="B177" t="s">
         <v>76</v>
       </c>
@@ -4015,13 +3493,10 @@
         <f>VLOOKUP(B177, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D177" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E177" s="3"/>
+      <c r="E177" s="2"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A178" s="26"/>
+      <c r="A178" s="20"/>
       <c r="B178" t="s">
         <v>127</v>
       </c>
@@ -4029,13 +3504,10 @@
         <f>VLOOKUP(B178, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E52</v>
       </c>
-      <c r="D178" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E178" s="3"/>
+      <c r="E178" s="2"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A179" s="26"/>
+      <c r="A179" s="20"/>
       <c r="B179" t="s">
         <v>128</v>
       </c>
@@ -4043,13 +3515,10 @@
         <f>VLOOKUP(B179, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E78</v>
       </c>
-      <c r="D179" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E179" s="3"/>
+      <c r="E179" s="2"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180" s="26"/>
+      <c r="A180" s="20"/>
       <c r="B180" t="s">
         <v>126</v>
       </c>
@@ -4057,13 +3526,10 @@
         <f>VLOOKUP(B180, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E93</v>
       </c>
-      <c r="D180" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E180" s="3"/>
+      <c r="E180" s="2"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A181" s="26"/>
+      <c r="A181" s="20"/>
       <c r="B181" t="s">
         <v>129</v>
       </c>
@@ -4071,13 +3537,10 @@
         <f>VLOOKUP(B181, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E60</v>
       </c>
-      <c r="D181" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E181" s="3"/>
+      <c r="E181" s="2"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182" s="26"/>
+      <c r="A182" s="20"/>
       <c r="B182" t="s">
         <v>7</v>
       </c>
@@ -4085,13 +3548,10 @@
         <f>VLOOKUP(B182, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D182" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E182" s="3"/>
+      <c r="E182" s="2"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183" s="26"/>
+      <c r="A183" s="20"/>
       <c r="B183" t="s">
         <v>130</v>
       </c>
@@ -4099,13 +3559,10 @@
         <f>VLOOKUP(B183, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E79</v>
       </c>
-      <c r="D183" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E183" s="3"/>
+      <c r="E183" s="2"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184" s="26"/>
+      <c r="A184" s="20"/>
       <c r="B184" t="s">
         <v>118</v>
       </c>
@@ -4113,13 +3570,10 @@
         <f>VLOOKUP(B184, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E94</v>
       </c>
-      <c r="D184" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E184" s="3"/>
+      <c r="E184" s="2"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A185" s="26"/>
+      <c r="A185" s="20"/>
       <c r="B185" t="s">
         <v>123</v>
       </c>
@@ -4127,13 +3581,10 @@
         <f>VLOOKUP(B185, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E97</v>
       </c>
-      <c r="D185" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E185" s="3"/>
+      <c r="E185" s="2"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A186" s="26"/>
+      <c r="A186" s="20"/>
       <c r="B186" t="s">
         <v>126</v>
       </c>
@@ -4141,13 +3592,10 @@
         <f>VLOOKUP(B186, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E93</v>
       </c>
-      <c r="D186" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E186" s="3"/>
+      <c r="E186" s="2"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A187" s="26"/>
+      <c r="A187" s="20"/>
       <c r="B187" t="s">
         <v>131</v>
       </c>
@@ -4155,13 +3603,10 @@
         <f>VLOOKUP(B187, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E77</v>
       </c>
-      <c r="D187" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E187" s="3"/>
+      <c r="E187" s="2"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188" s="26"/>
+      <c r="A188" s="20"/>
       <c r="B188" t="s">
         <v>76</v>
       </c>
@@ -4169,13 +3614,10 @@
         <f>VLOOKUP(B188, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E50</v>
       </c>
-      <c r="D188" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E188" s="3"/>
+      <c r="E188" s="2"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A189" s="26"/>
+      <c r="A189" s="20"/>
       <c r="B189" t="s">
         <v>7</v>
       </c>
@@ -4183,13 +3625,10 @@
         <f>VLOOKUP(B189, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D189" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E189" s="3"/>
+      <c r="E189" s="2"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A190" s="26"/>
+      <c r="A190" s="20"/>
       <c r="B190" t="s">
         <v>8</v>
       </c>
@@ -4197,13 +3636,10 @@
         <f>VLOOKUP(B190, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E47</v>
       </c>
-      <c r="D190" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E190" s="3"/>
+      <c r="E190" s="2"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A191" s="26"/>
+      <c r="A191" s="20"/>
       <c r="B191" t="s">
         <v>132</v>
       </c>
@@ -4211,13 +3647,10 @@
         <f>VLOOKUP(B191, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E43</v>
       </c>
-      <c r="D191" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E191" s="3"/>
+      <c r="E191" s="2"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A192" s="26"/>
+      <c r="A192" s="20"/>
       <c r="B192" t="s">
         <v>133</v>
       </c>
@@ -4225,13 +3658,10 @@
         <f>VLOOKUP(B192, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E80</v>
       </c>
-      <c r="D192" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E192" s="3"/>
+      <c r="E192" s="2"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A193" s="26"/>
+      <c r="A193" s="20"/>
       <c r="B193" t="s">
         <v>7</v>
       </c>
@@ -4239,13 +3669,10 @@
         <f>VLOOKUP(B193, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D193" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E193" s="3"/>
+      <c r="E193" s="2"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A194" s="26"/>
+      <c r="A194" s="20"/>
       <c r="B194" t="s">
         <v>123</v>
       </c>
@@ -4253,13 +3680,10 @@
         <f>VLOOKUP(B194, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E97</v>
       </c>
-      <c r="D194" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E194" s="3"/>
+      <c r="E194" s="2"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A195" s="26"/>
+      <c r="A195" s="20"/>
       <c r="B195" t="s">
         <v>118</v>
       </c>
@@ -4267,13 +3691,10 @@
         <f>VLOOKUP(B195, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E94</v>
       </c>
-      <c r="D195" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E195" s="3"/>
+      <c r="E195" s="2"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A196" s="26"/>
+      <c r="A196" s="20"/>
       <c r="B196" t="s">
         <v>154</v>
       </c>
@@ -4281,13 +3702,10 @@
         <f>VLOOKUP(B196, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E13</v>
       </c>
-      <c r="D196" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E196" s="3"/>
+      <c r="E196" s="2"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A197" s="26"/>
+      <c r="A197" s="20"/>
       <c r="B197" t="s">
         <v>125</v>
       </c>
@@ -4295,13 +3713,10 @@
         <f>VLOOKUP(B197, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E26</v>
       </c>
-      <c r="D197" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E197" s="3"/>
+      <c r="E197" s="2"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A198" s="26"/>
+      <c r="A198" s="20"/>
       <c r="B198" t="s">
         <v>134</v>
       </c>
@@ -4309,13 +3724,10 @@
         <f>VLOOKUP(B198, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E20</v>
       </c>
-      <c r="D198" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E198" s="3"/>
+      <c r="E198" s="2"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A199" s="26"/>
+      <c r="A199" s="20"/>
       <c r="B199" t="s">
         <v>135</v>
       </c>
@@ -4323,13 +3735,10 @@
         <f>VLOOKUP(B199, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E19</v>
       </c>
-      <c r="D199" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E199" s="3"/>
+      <c r="E199" s="2"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A200" s="26"/>
+      <c r="A200" s="20"/>
       <c r="B200" t="s">
         <v>136</v>
       </c>
@@ -4337,13 +3746,10 @@
         <f>VLOOKUP(B200, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E31</v>
       </c>
-      <c r="D200" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E200" s="3"/>
+      <c r="E200" s="2"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A201" s="26"/>
+      <c r="A201" s="20"/>
       <c r="B201" t="s">
         <v>117</v>
       </c>
@@ -4351,13 +3757,10 @@
         <f>VLOOKUP(B201, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E30</v>
       </c>
-      <c r="D201" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E201" s="3"/>
+      <c r="E201" s="2"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A202" s="26"/>
+      <c r="A202" s="20"/>
       <c r="B202" t="s">
         <v>155</v>
       </c>
@@ -4365,13 +3768,10 @@
         <f>VLOOKUP(B202, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E82</v>
       </c>
-      <c r="D202" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E202" s="3"/>
+      <c r="E202" s="2"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A203" s="26"/>
+      <c r="A203" s="20"/>
       <c r="B203" t="s">
         <v>143</v>
       </c>
@@ -4379,13 +3779,10 @@
         <f>VLOOKUP(B203, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E83</v>
       </c>
-      <c r="D203" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E203" s="3"/>
+      <c r="E203" s="2"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A204" s="26"/>
+      <c r="A204" s="20"/>
       <c r="B204" t="s">
         <v>23</v>
       </c>
@@ -4393,13 +3790,10 @@
         <f>VLOOKUP(B204, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E10</v>
       </c>
-      <c r="D204" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E204" s="3"/>
+      <c r="E204" s="2"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A205" s="26"/>
+      <c r="A205" s="20"/>
       <c r="B205" t="s">
         <v>156</v>
       </c>
@@ -4407,13 +3801,10 @@
         <f>VLOOKUP(B205, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E85</v>
       </c>
-      <c r="D205" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E205" s="3"/>
+      <c r="E205" s="2"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A206" s="26"/>
+      <c r="A206" s="20"/>
       <c r="B206" t="s">
         <v>19</v>
       </c>
@@ -4421,13 +3812,10 @@
         <f>VLOOKUP(B206, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E62</v>
       </c>
-      <c r="D206" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E206" s="3"/>
+      <c r="E206" s="2"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A207" s="26"/>
+      <c r="A207" s="20"/>
       <c r="B207" t="s">
         <v>137</v>
       </c>
@@ -4435,13 +3823,10 @@
         <f>VLOOKUP(B207, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E67</v>
       </c>
-      <c r="D207" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E207" s="3"/>
+      <c r="E207" s="2"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A208" s="26"/>
+      <c r="A208" s="20"/>
       <c r="B208" t="s">
         <v>82</v>
       </c>
@@ -4449,13 +3834,10 @@
         <f>VLOOKUP(B208, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E17</v>
       </c>
-      <c r="D208" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E208" s="3"/>
+      <c r="E208" s="2"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A209" s="26"/>
+      <c r="A209" s="20"/>
       <c r="B209" t="s">
         <v>138</v>
       </c>
@@ -4463,13 +3845,10 @@
         <f>VLOOKUP(B209, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E15</v>
       </c>
-      <c r="D209" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E209" s="3"/>
+      <c r="E209" s="2"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A210" s="26"/>
+      <c r="A210" s="20"/>
       <c r="B210" t="s">
         <v>135</v>
       </c>
@@ -4477,13 +3856,10 @@
         <f>VLOOKUP(B210, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E19</v>
       </c>
-      <c r="D210" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E210" s="3"/>
+      <c r="E210" s="2"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A211" s="26"/>
+      <c r="A211" s="20"/>
       <c r="B211" t="s">
         <v>139</v>
       </c>
@@ -4491,13 +3867,10 @@
         <f>VLOOKUP(B211, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E63</v>
       </c>
-      <c r="D211" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E211" s="3"/>
+      <c r="E211" s="2"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A212" s="26"/>
+      <c r="A212" s="20"/>
       <c r="B212" t="s">
         <v>135</v>
       </c>
@@ -4505,13 +3878,10 @@
         <f>VLOOKUP(B212, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E19</v>
       </c>
-      <c r="D212" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E212" s="3"/>
+      <c r="E212" s="2"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A213" s="26"/>
+      <c r="A213" s="20"/>
       <c r="B213" t="s">
         <v>140</v>
       </c>
@@ -4519,13 +3889,10 @@
         <f>VLOOKUP(B213, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E65</v>
       </c>
-      <c r="D213" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E213" s="3"/>
+      <c r="E213" s="2"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A214" s="26"/>
+      <c r="A214" s="20"/>
       <c r="B214" t="s">
         <v>136</v>
       </c>
@@ -4533,13 +3900,10 @@
         <f>VLOOKUP(B214, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E31</v>
       </c>
-      <c r="D214" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E214" s="3"/>
+      <c r="E214" s="2"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A215" s="26"/>
+      <c r="A215" s="20"/>
       <c r="B215" t="s">
         <v>7</v>
       </c>
@@ -4547,13 +3911,10 @@
         <f>VLOOKUP(B215, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E96</v>
       </c>
-      <c r="D215" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E215" s="3"/>
+      <c r="E215" s="2"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A216" s="26"/>
+      <c r="A216" s="20"/>
       <c r="B216" t="s">
         <v>82</v>
       </c>
@@ -4561,13 +3922,10 @@
         <f>VLOOKUP(B216, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E17</v>
       </c>
-      <c r="D216" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E216" s="3"/>
+      <c r="E216" s="2"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A217" s="26"/>
+      <c r="A217" s="20"/>
       <c r="B217" t="s">
         <v>135</v>
       </c>
@@ -4575,13 +3933,10 @@
         <f>VLOOKUP(B217, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E19</v>
       </c>
-      <c r="D217" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E217" s="3"/>
+      <c r="E217" s="2"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A218" s="26"/>
+      <c r="A218" s="20"/>
       <c r="B218" t="s">
         <v>123</v>
       </c>
@@ -4589,13 +3944,10 @@
         <f>VLOOKUP(B218, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E97</v>
       </c>
-      <c r="D218" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E218" s="3"/>
+      <c r="E218" s="2"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A219" s="26"/>
+      <c r="A219" s="20"/>
       <c r="B219" t="s">
         <v>141</v>
       </c>
@@ -4603,13 +3955,10 @@
         <f>VLOOKUP(B219, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E89</v>
       </c>
-      <c r="D219" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E219" s="3"/>
+      <c r="E219" s="2"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A220" s="26"/>
+      <c r="A220" s="20"/>
       <c r="B220" t="s">
         <v>101</v>
       </c>
@@ -4617,13 +3966,10 @@
         <f>VLOOKUP(B220, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E92</v>
       </c>
-      <c r="D220" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E220" s="3"/>
+      <c r="E220" s="2"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A221" s="26"/>
+      <c r="A221" s="20"/>
       <c r="B221" t="s">
         <v>135</v>
       </c>
@@ -4631,13 +3977,10 @@
         <f>VLOOKUP(B221, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E19</v>
       </c>
-      <c r="D221" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E221" s="3"/>
+      <c r="E221" s="2"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A222" s="26"/>
+      <c r="A222" s="20"/>
       <c r="B222" t="s">
         <v>123</v>
       </c>
@@ -4645,13 +3988,10 @@
         <f>VLOOKUP(B222, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E97</v>
       </c>
-      <c r="D222" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E222" s="3"/>
+      <c r="E222" s="2"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A223" s="26"/>
+      <c r="A223" s="20"/>
       <c r="B223" t="s">
         <v>157</v>
       </c>
@@ -4659,13 +3999,10 @@
         <f>VLOOKUP(B223, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E42</v>
       </c>
-      <c r="D223" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E223" s="3"/>
+      <c r="E223" s="2"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A224" s="26"/>
+      <c r="A224" s="20"/>
       <c r="B224" t="s">
         <v>135</v>
       </c>
@@ -4673,13 +4010,10 @@
         <f>VLOOKUP(B224, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E19</v>
       </c>
-      <c r="D224" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E224" s="3"/>
+      <c r="E224" s="2"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A225" s="26"/>
+      <c r="A225" s="20"/>
       <c r="B225" t="s">
         <v>140</v>
       </c>
@@ -4687,13 +4021,10 @@
         <f>VLOOKUP(B225, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E65</v>
       </c>
-      <c r="D225" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E225" s="3"/>
+      <c r="E225" s="2"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A226" s="26"/>
+      <c r="A226" s="20"/>
       <c r="B226" t="s">
         <v>122</v>
       </c>
@@ -4701,13 +4032,10 @@
         <f>VLOOKUP(B226, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E81</v>
       </c>
-      <c r="D226" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E226" s="3"/>
+      <c r="E226" s="2"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A227" s="26"/>
+      <c r="A227" s="20"/>
       <c r="B227" t="s">
         <v>123</v>
       </c>
@@ -4715,13 +4043,10 @@
         <f>VLOOKUP(B227, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E97</v>
       </c>
-      <c r="D227" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E227" s="3"/>
+      <c r="E227" s="2"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A228" s="26"/>
+      <c r="A228" s="20"/>
       <c r="B228" t="s">
         <v>111</v>
       </c>
@@ -4729,13 +4054,10 @@
         <f>VLOOKUP(B228, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E45</v>
       </c>
-      <c r="D228" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E228" s="3"/>
+      <c r="E228" s="2"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A229" s="26"/>
+      <c r="A229" s="20"/>
       <c r="B229" t="s">
         <v>133</v>
       </c>
@@ -4743,13 +4065,10 @@
         <f>VLOOKUP(B229, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E80</v>
       </c>
-      <c r="D229" s="3">
-        <v>3.7268518518518514E-3</v>
-      </c>
-      <c r="E229" s="3"/>
+      <c r="E229" s="2"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A230" s="26"/>
+      <c r="A230" s="20"/>
       <c r="B230" t="s">
         <v>128</v>
       </c>
@@ -4757,13 +4076,10 @@
         <f>VLOOKUP(B230, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E78</v>
       </c>
-      <c r="D230" s="3">
-        <v>5.6944444444444438E-3</v>
-      </c>
-      <c r="E230" s="3"/>
+      <c r="E230" s="2"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A231" s="26"/>
+      <c r="A231" s="20"/>
       <c r="B231" t="s">
         <v>129</v>
       </c>
@@ -4771,13 +4087,10 @@
         <f>VLOOKUP(B231, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E60</v>
       </c>
-      <c r="D231" s="3">
-        <v>0.96729166666666699</v>
-      </c>
-      <c r="E231" s="3"/>
+      <c r="E231" s="2"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A232" s="26"/>
+      <c r="A232" s="20"/>
       <c r="B232" t="s">
         <v>123</v>
       </c>
@@ -4785,13 +4098,10 @@
         <f>VLOOKUP(B232, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E97</v>
       </c>
-      <c r="D232" s="3">
-        <v>1.0089583333333301</v>
-      </c>
-      <c r="E232" s="3"/>
+      <c r="E232" s="2"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A233" s="26"/>
+      <c r="A233" s="20"/>
       <c r="B233" t="s">
         <v>133</v>
       </c>
@@ -4799,24 +4109,20 @@
         <f>VLOOKUP(B233, 'Asignar letras'!$A$2:$B$100, 2, 0)</f>
         <v>E80</v>
       </c>
-      <c r="D233" s="3">
-        <v>1.0506249999999999</v>
-      </c>
-      <c r="E233" s="3"/>
+      <c r="E233" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
+    <mergeCell ref="A4:A28"/>
+    <mergeCell ref="A29:A46"/>
+    <mergeCell ref="A47:A67"/>
+    <mergeCell ref="A68:A86"/>
     <mergeCell ref="A166:A233"/>
     <mergeCell ref="A87:A96"/>
     <mergeCell ref="A97:A114"/>
     <mergeCell ref="A147:A165"/>
     <mergeCell ref="A115:A133"/>
     <mergeCell ref="A134:A146"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="A4:A28"/>
-    <mergeCell ref="A29:A46"/>
-    <mergeCell ref="A47:A67"/>
-    <mergeCell ref="A68:A86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4824,7 +4130,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:Q43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4834,41 +4140,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="9" t="s">
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="10">
+      <c r="D3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="9">
         <v>1</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="13">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="M3" t="s">
@@ -4882,23 +4188,23 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="31"/>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="26"/>
+      <c r="B4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="10">
+      <c r="D4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="9">
         <v>2</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="14">
         <v>2.199074074074074E-4</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>32</v>
       </c>
       <c r="M4" t="s">
@@ -4912,23 +4218,23 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="26"/>
+      <c r="B5" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="10">
+      <c r="D5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="9">
         <v>3</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="14">
         <v>3.0324074074074073E-3</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>33</v>
       </c>
       <c r="M5" t="s">
@@ -4942,23 +4248,23 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="31"/>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="26"/>
+      <c r="B6" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C6" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="10">
+      <c r="D6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="9">
         <v>4</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="14">
         <v>8.1249999999999985E-3</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>52</v>
       </c>
       <c r="M6" t="s">
@@ -4969,23 +4275,23 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="31"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="26"/>
+      <c r="B7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="10">
+      <c r="D7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="9">
         <v>5</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <v>8.9583333333333338E-3</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>33</v>
       </c>
       <c r="M7" t="s">
@@ -4999,21 +4305,21 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="31"/>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="26"/>
+      <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="10">
+      <c r="D8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="9">
         <v>6</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="6" t="s">
+      <c r="F8" s="14"/>
+      <c r="G8" s="5" t="s">
         <v>52</v>
       </c>
       <c r="M8" t="s">
@@ -5024,21 +4330,21 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="31"/>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="26"/>
+      <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C9" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="10">
+      <c r="D9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="9">
         <v>7</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="6" t="s">
+      <c r="F9" s="4"/>
+      <c r="G9" s="5" t="s">
         <v>53</v>
       </c>
       <c r="M9" t="s">
@@ -5049,21 +4355,21 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="31"/>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="26"/>
+      <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="10">
+      <c r="D10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="9">
         <v>8</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="6" t="s">
+      <c r="F10" s="4"/>
+      <c r="G10" s="5" t="s">
         <v>54</v>
       </c>
       <c r="M10" t="s">
@@ -5074,21 +4380,21 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="31"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="26"/>
+      <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C11" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="10">
+      <c r="D11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="9">
         <v>9</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="4"/>
+      <c r="G11" s="5" t="s">
         <v>53</v>
       </c>
       <c r="M11" t="s">
@@ -5099,21 +4405,21 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="31"/>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="26"/>
+      <c r="B12" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="10">
+      <c r="D12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="9">
         <v>10</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6" t="s">
+      <c r="F12" s="4"/>
+      <c r="G12" s="5" t="s">
         <v>32</v>
       </c>
       <c r="M12" t="s">
@@ -5127,21 +4433,21 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="31"/>
-      <c r="B13" s="5" t="s">
+      <c r="A13" s="26"/>
+      <c r="B13" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="10">
+      <c r="D13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="9">
         <v>11</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6" t="s">
+      <c r="F13" s="4"/>
+      <c r="G13" s="5" t="s">
         <v>33</v>
       </c>
       <c r="M13" t="s">
@@ -5155,21 +4461,21 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="26"/>
+      <c r="B14" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="10">
+      <c r="D14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="9">
         <v>12</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="6" t="s">
+      <c r="F14" s="4"/>
+      <c r="G14" s="5" t="s">
         <v>53</v>
       </c>
       <c r="M14" t="s">
@@ -5180,21 +4486,21 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="31"/>
-      <c r="B15" s="5" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="10">
+      <c r="D15" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="9">
         <v>13</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="6" t="s">
+      <c r="F15" s="4"/>
+      <c r="G15" s="5" t="s">
         <v>55</v>
       </c>
       <c r="M15" t="s">
@@ -5205,21 +4511,21 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
-      <c r="B16" s="5" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="10">
+      <c r="D16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="9">
         <v>14</v>
       </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="6" t="s">
+      <c r="F16" s="4"/>
+      <c r="G16" s="5" t="s">
         <v>32</v>
       </c>
       <c r="M16" t="s">
@@ -5233,21 +4539,21 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="31"/>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="26"/>
+      <c r="B17" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="10">
+      <c r="D17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="9">
         <v>15</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="6" t="s">
+      <c r="F17" s="4"/>
+      <c r="G17" s="5" t="s">
         <v>56</v>
       </c>
       <c r="M17" t="s">
@@ -5258,21 +4564,21 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
-      <c r="B18" s="5" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="10">
+      <c r="D18" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="9">
         <v>16</v>
       </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="6" t="s">
+      <c r="F18" s="4"/>
+      <c r="G18" s="5" t="s">
         <v>40</v>
       </c>
       <c r="M18" t="s">
@@ -5292,21 +4598,21 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="31"/>
-      <c r="B19" s="5" t="s">
+      <c r="A19" s="26"/>
+      <c r="B19" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="10">
+      <c r="D19" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="9">
         <v>17</v>
       </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="6" t="s">
+      <c r="F19" s="4"/>
+      <c r="G19" s="5" t="s">
         <v>43</v>
       </c>
       <c r="M19" t="s">
@@ -5320,21 +4626,21 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="31"/>
-      <c r="B20" s="5" t="s">
+      <c r="A20" s="26"/>
+      <c r="B20" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C20" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" s="10">
+      <c r="D20" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="9">
         <v>18</v>
       </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="6" t="s">
+      <c r="F20" s="4"/>
+      <c r="G20" s="5" t="s">
         <v>57</v>
       </c>
       <c r="M20" t="s">
@@ -5345,21 +4651,21 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="31"/>
-      <c r="B21" s="5" t="s">
+      <c r="A21" s="26"/>
+      <c r="B21" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C21" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="10">
+      <c r="D21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="9">
         <v>19</v>
       </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="6" t="s">
+      <c r="F21" s="4"/>
+      <c r="G21" s="5" t="s">
         <v>43</v>
       </c>
       <c r="M21" t="s">
@@ -5373,21 +4679,21 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="31"/>
-      <c r="B22" s="5" t="s">
+      <c r="A22" s="26"/>
+      <c r="B22" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C22" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="10">
+      <c r="D22" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="9">
         <v>20</v>
       </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="6" t="s">
+      <c r="F22" s="4"/>
+      <c r="G22" s="5" t="s">
         <v>52</v>
       </c>
       <c r="M22" t="s">
@@ -5398,21 +4704,21 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="31"/>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="26"/>
+      <c r="B23" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C23" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E23" s="10">
+      <c r="D23" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="9">
         <v>21</v>
       </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="6" t="s">
+      <c r="F23" s="4"/>
+      <c r="G23" s="5" t="s">
         <v>53</v>
       </c>
       <c r="M23" t="s">
@@ -5423,21 +4729,21 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="31"/>
-      <c r="B24" s="5" t="s">
+      <c r="A24" s="26"/>
+      <c r="B24" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C24" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="10">
+      <c r="D24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="9">
         <v>22</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="6" t="s">
+      <c r="F24" s="4"/>
+      <c r="G24" s="5" t="s">
         <v>33</v>
       </c>
       <c r="M24" t="s">
@@ -5451,21 +4757,21 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="31"/>
-      <c r="B25" s="5" t="s">
+      <c r="A25" s="26"/>
+      <c r="B25" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C25" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25" s="10">
+      <c r="D25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="9">
         <v>23</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="6" t="s">
+      <c r="F25" s="4"/>
+      <c r="G25" s="5" t="s">
         <v>53</v>
       </c>
       <c r="M25" t="s">
@@ -5476,21 +4782,21 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="31"/>
-      <c r="B26" s="5" t="s">
+      <c r="A26" s="26"/>
+      <c r="B26" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C26" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E26" s="10">
+      <c r="D26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="9">
         <v>24</v>
       </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="6" t="s">
+      <c r="F26" s="4"/>
+      <c r="G26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="M26" t="s">
@@ -5504,21 +4810,21 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="31"/>
-      <c r="B27" s="5" t="s">
+      <c r="A27" s="26"/>
+      <c r="B27" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E27" s="10">
+      <c r="D27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="9">
         <v>25</v>
       </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="6" t="s">
+      <c r="F27" s="4"/>
+      <c r="G27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="M27" t="s">
@@ -5532,23 +4838,23 @@
       </c>
     </row>
     <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28" s="18">
+      <c r="D28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="17">
         <v>26</v>
       </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="17" t="s">
+      <c r="F28" s="15"/>
+      <c r="G28" s="16" t="s">
         <v>55</v>
       </c>
       <c r="M28" t="s">
@@ -5559,21 +4865,21 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="31"/>
-      <c r="B29" s="5" t="s">
+      <c r="A29" s="26"/>
+      <c r="B29" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C29" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E29" s="10">
+      <c r="D29" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="9">
         <v>27</v>
       </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="6" t="s">
+      <c r="F29" s="4"/>
+      <c r="G29" s="5" t="s">
         <v>33</v>
       </c>
       <c r="M29" t="s">
@@ -5587,21 +4893,21 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="31"/>
-      <c r="B30" s="5" t="s">
+      <c r="A30" s="26"/>
+      <c r="B30" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C30" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="10">
+      <c r="D30" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="9">
         <v>28</v>
       </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="6" t="s">
+      <c r="F30" s="4"/>
+      <c r="G30" s="5" t="s">
         <v>52</v>
       </c>
       <c r="M30" t="s">
@@ -5612,21 +4918,21 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="31"/>
-      <c r="B31" s="5" t="s">
+      <c r="A31" s="26"/>
+      <c r="B31" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C31" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31" s="10">
+      <c r="D31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="9">
         <v>29</v>
       </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="6" t="s">
+      <c r="F31" s="4"/>
+      <c r="G31" s="5" t="s">
         <v>54</v>
       </c>
       <c r="M31" t="s">
@@ -5637,21 +4943,21 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="31"/>
-      <c r="B32" s="5" t="s">
+      <c r="A32" s="26"/>
+      <c r="B32" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C32" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="10">
+      <c r="D32" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="9">
         <v>30</v>
       </c>
-      <c r="F32" s="5"/>
-      <c r="G32" s="6" t="s">
+      <c r="F32" s="4"/>
+      <c r="G32" s="5" t="s">
         <v>43</v>
       </c>
       <c r="M32" t="s">
@@ -5665,23 +4971,23 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="31"/>
-      <c r="B33" s="5" t="s">
+      <c r="A33" s="26"/>
+      <c r="B33" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C33" t="s">
         <v>51</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="10">
+      <c r="D33" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="9">
         <v>31</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="14">
         <v>3.7268518518518514E-3</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="5" t="s">
         <v>58</v>
       </c>
       <c r="M33" t="s">
@@ -5692,23 +4998,23 @@
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="31"/>
-      <c r="B34" s="5" t="s">
+      <c r="A34" s="26"/>
+      <c r="B34" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C34" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="10">
+      <c r="D34" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="9">
         <v>31</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="14">
         <v>3.7268518518518514E-3</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="5" t="s">
         <v>58</v>
       </c>
       <c r="M34" t="s">
@@ -5719,23 +5025,23 @@
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="31"/>
-      <c r="B35" s="5" t="s">
+      <c r="A35" s="26"/>
+      <c r="B35" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C35" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="10">
+      <c r="D35" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="9">
         <v>32</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="14">
         <v>5.6944444444444438E-3</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="5" t="s">
         <v>54</v>
       </c>
       <c r="M35" t="s">
@@ -5746,21 +5052,21 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" s="31"/>
-      <c r="B36" s="5" t="s">
+      <c r="A36" s="26"/>
+      <c r="B36" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C36" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="10">
+      <c r="D36" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="9">
         <v>34</v>
       </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="6" t="s">
+      <c r="F36" s="4"/>
+      <c r="G36" s="5" t="s">
         <v>40</v>
       </c>
       <c r="M36" t="s">
@@ -5780,21 +5086,21 @@
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A37" s="31"/>
-      <c r="B37" s="5" t="s">
+      <c r="A37" s="26"/>
+      <c r="B37" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C37" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="10">
+      <c r="D37" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="9">
         <v>35</v>
       </c>
-      <c r="F37" s="5"/>
-      <c r="G37" s="6" t="s">
+      <c r="F37" s="4"/>
+      <c r="G37" s="5" t="s">
         <v>45</v>
       </c>
       <c r="M37" t="s">
@@ -5808,21 +5114,21 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" s="31"/>
-      <c r="B38" s="5" t="s">
+      <c r="A38" s="26"/>
+      <c r="B38" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C38" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E38" s="10">
+      <c r="D38" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="9">
         <v>36</v>
       </c>
-      <c r="F38" s="5"/>
-      <c r="G38" s="6" t="s">
+      <c r="F38" s="4"/>
+      <c r="G38" s="5" t="s">
         <v>43</v>
       </c>
       <c r="M38" t="s">
@@ -5836,21 +5142,21 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" s="31"/>
-      <c r="B39" s="5" t="s">
+      <c r="A39" s="26"/>
+      <c r="B39" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C39" t="s">
         <v>30</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E39" s="10">
+      <c r="D39" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="9">
         <v>37</v>
       </c>
-      <c r="F39" s="5"/>
-      <c r="G39" s="6" t="s">
+      <c r="F39" s="4"/>
+      <c r="G39" s="5" t="s">
         <v>40</v>
       </c>
       <c r="M39" t="s">
@@ -5870,21 +5176,21 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="31"/>
-      <c r="B40" s="5" t="s">
+      <c r="A40" s="26"/>
+      <c r="B40" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C40" t="s">
         <v>34</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E40" s="10">
+      <c r="D40" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="9">
         <v>38</v>
       </c>
-      <c r="F40" s="5"/>
-      <c r="G40" s="6" t="s">
+      <c r="F40" s="4"/>
+      <c r="G40" s="5" t="s">
         <v>43</v>
       </c>
       <c r="M40" t="s">
@@ -5898,21 +5204,21 @@
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="31"/>
-      <c r="B41" s="5" t="s">
+      <c r="A41" s="26"/>
+      <c r="B41" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C41" t="s">
         <v>51</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" s="10">
+      <c r="D41" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" s="9">
         <v>39</v>
       </c>
-      <c r="F41" s="5"/>
-      <c r="G41" s="6" t="s">
+      <c r="F41" s="4"/>
+      <c r="G41" s="5" t="s">
         <v>45</v>
       </c>
       <c r="M41" t="s">
@@ -5926,21 +5232,21 @@
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="31"/>
-      <c r="B42" s="5" t="s">
+      <c r="A42" s="26"/>
+      <c r="B42" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C42" t="s">
         <v>51</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" s="10">
+      <c r="D42" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="9">
         <v>40</v>
       </c>
-      <c r="F42" s="5"/>
-      <c r="G42" s="6" t="s">
+      <c r="F42" s="4"/>
+      <c r="G42" s="5" t="s">
         <v>59</v>
       </c>
       <c r="M42" t="s">
@@ -5951,21 +5257,21 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A43" s="31"/>
-      <c r="B43" s="7" t="s">
+      <c r="A43" s="26"/>
+      <c r="B43" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E43" s="11">
+      <c r="C43" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="10">
         <v>41</v>
       </c>
-      <c r="F43" s="7"/>
-      <c r="G43" s="6" t="s">
+      <c r="F43" s="6"/>
+      <c r="G43" s="5" t="s">
         <v>60</v>
       </c>
       <c r="M43" t="s">
@@ -5988,7 +5294,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:B100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6012,7 +5318,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" t="s">
         <v>85</v>
       </c>
       <c r="B4" t="s">
@@ -6052,7 +5358,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+      <c r="A9" t="s">
         <v>144</v>
       </c>
       <c r="B9" t="s">
@@ -6188,7 +5494,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>89</v>
       </c>
       <c r="B26" t="s">
@@ -6332,7 +5638,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>132</v>
       </c>
       <c r="B44" t="s">
@@ -6444,7 +5750,7 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="21" t="s">
+      <c r="A58" t="s">
         <v>6</v>
       </c>
       <c r="B58" t="s">
@@ -6556,7 +5862,7 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="21" t="s">
+      <c r="A72" t="s">
         <v>70</v>
       </c>
       <c r="B72" t="s">
@@ -6788,7 +6094,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:B100">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B100">
     <sortCondition ref="A2:A100"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
